--- a/research/traditional_assets/database/data/peru/peru_retail_general.xlsx
+++ b/research/traditional_assets/database/data/peru/peru_retail_general.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1078944736735083</v>
+        <v>0.1076079099761715</v>
       </c>
       <c r="C2">
-        <v>5347.414893669069</v>
+        <v>5310.845905957366</v>
       </c>
       <c r="D2">
-        <v>5065.614893669069</v>
+        <v>5089.100905957366</v>
       </c>
       <c r="E2">
-        <v>-2608.3</v>
+        <v>-2548.245</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>60.055</v>
       </c>
       <c r="G2">
         <v>281.8</v>
@@ -1457,28 +1457,28 @@
         <v>729.875</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.0207665</v>
       </c>
       <c r="N2">
-        <v>729.875</v>
+        <v>726.8542335</v>
       </c>
       <c r="O2">
-        <v>215.313125</v>
+        <v>214.4219988825</v>
       </c>
       <c r="P2">
-        <v>514.561875</v>
+        <v>512.4322346174999</v>
       </c>
       <c r="Q2">
-        <v>690.561875</v>
+        <v>688.4322346174999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1078944736735083</v>
+        <v>0.1083366615920924</v>
       </c>
       <c r="T2">
-        <v>0.960581759320096</v>
+        <v>0.9674222657879815</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>241.6191387186001</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1076079099761715</v>
+        <v>0.1073213462788346</v>
       </c>
       <c r="C3">
-        <v>5310.845905957366</v>
+        <v>5274.495711848996</v>
       </c>
       <c r="D3">
-        <v>5089.100905957366</v>
+        <v>5112.805711848995</v>
       </c>
       <c r="E3">
-        <v>-2548.245</v>
+        <v>-2488.19</v>
       </c>
       <c r="F3">
-        <v>60.055</v>
+        <v>120.11</v>
       </c>
       <c r="G3">
         <v>281.8</v>
@@ -1539,28 +1539,28 @@
         <v>729.875</v>
       </c>
       <c r="M3">
-        <v>3.0207665</v>
+        <v>6.041532999999999</v>
       </c>
       <c r="N3">
-        <v>726.8542335</v>
+        <v>723.833467</v>
       </c>
       <c r="O3">
-        <v>214.4219988825</v>
+        <v>213.530872765</v>
       </c>
       <c r="P3">
-        <v>512.4322346174999</v>
+        <v>510.302594235</v>
       </c>
       <c r="Q3">
-        <v>688.4322346174999</v>
+        <v>686.302594235</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1083366615920924</v>
+        <v>0.1087878737539129</v>
       </c>
       <c r="T3">
-        <v>0.9674222657879815</v>
+        <v>0.9744023744286811</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>241.6191387186001</v>
+        <v>120.8095693593001</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1073213462788346</v>
+        <v>0.1070347825814977</v>
       </c>
       <c r="C4">
-        <v>5274.495711848996</v>
+        <v>5238.367383044448</v>
       </c>
       <c r="D4">
-        <v>5112.805711848995</v>
+        <v>5136.732383044447</v>
       </c>
       <c r="E4">
-        <v>-2488.19</v>
+        <v>-2428.135</v>
       </c>
       <c r="F4">
-        <v>120.11</v>
+        <v>180.165</v>
       </c>
       <c r="G4">
         <v>281.8</v>
@@ -1621,28 +1621,28 @@
         <v>729.875</v>
       </c>
       <c r="M4">
-        <v>6.041532999999999</v>
+        <v>9.0622995</v>
       </c>
       <c r="N4">
-        <v>723.833467</v>
+        <v>720.8127005</v>
       </c>
       <c r="O4">
-        <v>213.530872765</v>
+        <v>212.6397466475</v>
       </c>
       <c r="P4">
-        <v>510.302594235</v>
+        <v>508.1729538525</v>
       </c>
       <c r="Q4">
-        <v>686.302594235</v>
+        <v>684.1729538525</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1087878737539129</v>
+        <v>0.109248389259276</v>
       </c>
       <c r="T4">
-        <v>0.9744023744286811</v>
+        <v>0.9815264028351682</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>120.8095693593001</v>
+        <v>80.53971290620002</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1070347825814977</v>
+        <v>0.1067482188841609</v>
       </c>
       <c r="C5">
-        <v>5238.367383044448</v>
+        <v>5202.464049013765</v>
       </c>
       <c r="D5">
-        <v>5136.732383044447</v>
+        <v>5160.884049013765</v>
       </c>
       <c r="E5">
-        <v>-2428.135</v>
+        <v>-2368.08</v>
       </c>
       <c r="F5">
-        <v>180.165</v>
+        <v>240.22</v>
       </c>
       <c r="G5">
         <v>281.8</v>
@@ -1703,28 +1703,28 @@
         <v>729.875</v>
       </c>
       <c r="M5">
-        <v>9.0622995</v>
+        <v>12.083066</v>
       </c>
       <c r="N5">
-        <v>720.8127005</v>
+        <v>717.791934</v>
       </c>
       <c r="O5">
-        <v>212.6397466475</v>
+        <v>211.74862053</v>
       </c>
       <c r="P5">
-        <v>508.1729538525</v>
+        <v>506.04331347</v>
       </c>
       <c r="Q5">
-        <v>684.1729538525</v>
+        <v>682.0433134699999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.109248389259276</v>
+        <v>0.1097184988376676</v>
       </c>
       <c r="T5">
-        <v>0.9815264028351682</v>
+        <v>0.9887988485001238</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>80.53971290620002</v>
+        <v>60.40478467965002</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1067482188841609</v>
+        <v>0.1064616551868241</v>
       </c>
       <c r="C6">
-        <v>5202.464049013765</v>
+        <v>5166.788898361056</v>
       </c>
       <c r="D6">
-        <v>5160.884049013765</v>
+        <v>5185.263898361056</v>
       </c>
       <c r="E6">
-        <v>-2368.08</v>
+        <v>-2308.025</v>
       </c>
       <c r="F6">
-        <v>240.22</v>
+        <v>300.275</v>
       </c>
       <c r="G6">
         <v>281.8</v>
@@ -1785,28 +1785,28 @@
         <v>729.875</v>
       </c>
       <c r="M6">
-        <v>12.083066</v>
+        <v>15.1038325</v>
       </c>
       <c r="N6">
-        <v>717.791934</v>
+        <v>714.7711675</v>
       </c>
       <c r="O6">
-        <v>211.74862053</v>
+        <v>210.8574944125</v>
       </c>
       <c r="P6">
-        <v>506.04331347</v>
+        <v>503.9136730875001</v>
       </c>
       <c r="Q6">
-        <v>682.0433134699999</v>
+        <v>679.9136730875</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1097184988376676</v>
+        <v>0.1101985054598148</v>
       </c>
       <c r="T6">
-        <v>0.9887988485001238</v>
+        <v>0.9962243982843417</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>60.40478467965002</v>
+        <v>48.32382774372001</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1064616551868241</v>
+        <v>0.1061750914894872</v>
       </c>
       <c r="C7">
-        <v>5166.788898361056</v>
+        <v>5131.345180227859</v>
       </c>
       <c r="D7">
-        <v>5185.263898361056</v>
+        <v>5209.875180227858</v>
       </c>
       <c r="E7">
-        <v>-2308.025</v>
+        <v>-2247.97</v>
       </c>
       <c r="F7">
-        <v>300.275</v>
+        <v>360.33</v>
       </c>
       <c r="G7">
         <v>281.8</v>
@@ -1867,28 +1867,28 @@
         <v>729.875</v>
       </c>
       <c r="M7">
-        <v>15.1038325</v>
+        <v>18.124599</v>
       </c>
       <c r="N7">
-        <v>714.7711675</v>
+        <v>711.750401</v>
       </c>
       <c r="O7">
-        <v>210.8574944125</v>
+        <v>209.966368295</v>
       </c>
       <c r="P7">
-        <v>503.9136730875001</v>
+        <v>501.784032705</v>
       </c>
       <c r="Q7">
-        <v>679.9136730875</v>
+        <v>677.7840327050001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1101985054598148</v>
+        <v>0.1106887249888162</v>
       </c>
       <c r="T7">
-        <v>0.9962243982843417</v>
+        <v>1.0038079384895</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>48.32382774372001</v>
+        <v>40.26985645310001</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1061750914894872</v>
+        <v>0.1058885277921504</v>
       </c>
       <c r="C8">
-        <v>5131.345180227859</v>
+        <v>5096.136205736649</v>
       </c>
       <c r="D8">
-        <v>5209.875180227858</v>
+        <v>5234.721205736649</v>
       </c>
       <c r="E8">
-        <v>-2247.97</v>
+        <v>-2187.915</v>
       </c>
       <c r="F8">
-        <v>360.33</v>
+        <v>420.3849999999999</v>
       </c>
       <c r="G8">
         <v>281.8</v>
@@ -1949,28 +1949,28 @@
         <v>729.875</v>
       </c>
       <c r="M8">
-        <v>18.124599</v>
+        <v>21.1453655</v>
       </c>
       <c r="N8">
-        <v>711.750401</v>
+        <v>708.7296345</v>
       </c>
       <c r="O8">
-        <v>209.966368295</v>
+        <v>209.0752421775</v>
       </c>
       <c r="P8">
-        <v>501.784032705</v>
+        <v>499.6543923225</v>
       </c>
       <c r="Q8">
-        <v>677.7840327050001</v>
+        <v>675.6543923225</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1106887249888162</v>
+        <v>0.11118948687328</v>
       </c>
       <c r="T8">
-        <v>1.0038079384895</v>
+        <v>1.011554565580791</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>40.26985645310001</v>
+        <v>34.51701981694287</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1058885277921504</v>
+        <v>0.1056019640948135</v>
       </c>
       <c r="C9">
-        <v>5096.13620573665</v>
+        <v>5061.165349475896</v>
       </c>
       <c r="D9">
-        <v>5234.72120573665</v>
+        <v>5259.805349475895</v>
       </c>
       <c r="E9">
-        <v>-2187.915</v>
+        <v>-2127.86</v>
       </c>
       <c r="F9">
-        <v>420.385</v>
+        <v>480.44</v>
       </c>
       <c r="G9">
         <v>281.8</v>
@@ -2031,28 +2031,28 @@
         <v>729.875</v>
       </c>
       <c r="M9">
-        <v>21.1453655</v>
+        <v>24.166132</v>
       </c>
       <c r="N9">
-        <v>708.7296345</v>
+        <v>705.7088680000001</v>
       </c>
       <c r="O9">
-        <v>209.0752421775</v>
+        <v>208.18411606</v>
       </c>
       <c r="P9">
-        <v>499.6543923225</v>
+        <v>497.52475194</v>
       </c>
       <c r="Q9">
-        <v>675.6543923225</v>
+        <v>673.52475194</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.11118948687328</v>
+        <v>0.1117011348856669</v>
       </c>
       <c r="T9">
-        <v>1.011554565580791</v>
+        <v>1.01946959760885</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>34.51701981694286</v>
+        <v>30.20239233982501</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1056019640948135</v>
+        <v>0.1053154003974767</v>
       </c>
       <c r="C10">
-        <v>5061.165349475896</v>
+        <v>5026.436051027957</v>
       </c>
       <c r="D10">
-        <v>5259.805349475895</v>
+        <v>5285.131051027956</v>
       </c>
       <c r="E10">
-        <v>-2127.86</v>
+        <v>-2067.805</v>
       </c>
       <c r="F10">
-        <v>480.44</v>
+        <v>540.495</v>
       </c>
       <c r="G10">
         <v>281.8</v>
@@ -2113,28 +2113,28 @@
         <v>729.875</v>
       </c>
       <c r="M10">
-        <v>24.166132</v>
+        <v>27.1868985</v>
       </c>
       <c r="N10">
-        <v>705.7088680000001</v>
+        <v>702.6881015</v>
       </c>
       <c r="O10">
-        <v>208.18411606</v>
+        <v>207.2929899425</v>
       </c>
       <c r="P10">
-        <v>497.52475194</v>
+        <v>495.3951115575001</v>
       </c>
       <c r="Q10">
-        <v>673.52475194</v>
+        <v>671.3951115575001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1117011348856669</v>
+        <v>0.112224027909315</v>
       </c>
       <c r="T10">
-        <v>1.01946959760885</v>
+        <v>1.027558586384778</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>30.20239233982501</v>
+        <v>26.84657096873334</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1053154003974767</v>
+        <v>0.1050288367001398</v>
       </c>
       <c r="C11">
-        <v>5026.436051027957</v>
+        <v>4991.951816541386</v>
       </c>
       <c r="D11">
-        <v>5285.131051027956</v>
+        <v>5310.701816541386</v>
       </c>
       <c r="E11">
-        <v>-2067.805</v>
+        <v>-2007.75</v>
       </c>
       <c r="F11">
-        <v>540.495</v>
+        <v>600.55</v>
       </c>
       <c r="G11">
         <v>281.8</v>
@@ -2195,28 +2195,28 @@
         <v>729.875</v>
       </c>
       <c r="M11">
-        <v>27.1868985</v>
+        <v>30.207665</v>
       </c>
       <c r="N11">
-        <v>702.6881015</v>
+        <v>699.667335</v>
       </c>
       <c r="O11">
-        <v>207.2929899425</v>
+        <v>206.401863825</v>
       </c>
       <c r="P11">
-        <v>495.3951115575001</v>
+        <v>493.265471175</v>
       </c>
       <c r="Q11">
-        <v>671.3951115575001</v>
+        <v>669.265471175</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.112224027909315</v>
+        <v>0.1127585407779331</v>
       </c>
       <c r="T11">
-        <v>1.027558586384778</v>
+        <v>1.035827330466837</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>26.84657096873334</v>
+        <v>24.16191387186001</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1050288367001398</v>
+        <v>0.1047422730028029</v>
       </c>
       <c r="C12">
-        <v>4991.951816541386</v>
+        <v>4957.716220349061</v>
       </c>
       <c r="D12">
-        <v>5310.701816541386</v>
+        <v>5336.521220349061</v>
       </c>
       <c r="E12">
-        <v>-2007.75</v>
+        <v>-1947.695</v>
       </c>
       <c r="F12">
-        <v>600.5500000000001</v>
+        <v>660.605</v>
       </c>
       <c r="G12">
         <v>281.8</v>
@@ -2277,28 +2277,28 @@
         <v>729.875</v>
       </c>
       <c r="M12">
-        <v>30.207665</v>
+        <v>33.2284315</v>
       </c>
       <c r="N12">
-        <v>699.667335</v>
+        <v>696.6465685000001</v>
       </c>
       <c r="O12">
-        <v>206.401863825</v>
+        <v>205.5107377075</v>
       </c>
       <c r="P12">
-        <v>493.265471175</v>
+        <v>491.1358307925001</v>
       </c>
       <c r="Q12">
-        <v>669.265471175</v>
+        <v>667.1358307925001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1127585407779331</v>
+        <v>0.1133050651716887</v>
       </c>
       <c r="T12">
-        <v>1.035827330466837</v>
+        <v>1.04428188902265</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>24.16191387186</v>
+        <v>21.96537624714546</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1047422730028029</v>
+        <v>0.1044557093054661</v>
       </c>
       <c r="C13">
-        <v>4957.716220349061</v>
+        <v>4923.73290663378</v>
       </c>
       <c r="D13">
-        <v>5336.521220349061</v>
+        <v>5362.592906633779</v>
       </c>
       <c r="E13">
-        <v>-1947.695</v>
+        <v>-1887.64</v>
       </c>
       <c r="F13">
-        <v>660.605</v>
+        <v>720.66</v>
       </c>
       <c r="G13">
         <v>281.8</v>
@@ -2359,28 +2359,28 @@
         <v>729.875</v>
       </c>
       <c r="M13">
-        <v>33.2284315</v>
+        <v>36.249198</v>
       </c>
       <c r="N13">
-        <v>696.6465685000001</v>
+        <v>693.625802</v>
       </c>
       <c r="O13">
-        <v>205.5107377075</v>
+        <v>204.61961159</v>
       </c>
       <c r="P13">
-        <v>491.1358307925001</v>
+        <v>489.00619041</v>
       </c>
       <c r="Q13">
-        <v>667.1358307925001</v>
+        <v>665.00619041</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1133050651716887</v>
+        <v>0.1138640105743933</v>
       </c>
       <c r="T13">
-        <v>1.04428188902265</v>
+        <v>1.052928596636551</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>21.96537624714546</v>
+        <v>20.13492822655001</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1044557093054661</v>
+        <v>0.1041691456081293</v>
       </c>
       <c r="C14">
-        <v>4923.73290663378</v>
+        <v>4890.005591142891</v>
       </c>
       <c r="D14">
-        <v>5362.592906633779</v>
+        <v>5388.920591142891</v>
       </c>
       <c r="E14">
-        <v>-1887.64</v>
+        <v>-1827.585</v>
       </c>
       <c r="F14">
-        <v>720.66</v>
+        <v>780.715</v>
       </c>
       <c r="G14">
         <v>281.8</v>
@@ -2441,28 +2441,28 @@
         <v>729.875</v>
       </c>
       <c r="M14">
-        <v>36.249198</v>
+        <v>39.2699645</v>
       </c>
       <c r="N14">
-        <v>693.625802</v>
+        <v>690.6050355</v>
       </c>
       <c r="O14">
-        <v>204.61961159</v>
+        <v>203.7284854725</v>
       </c>
       <c r="P14">
-        <v>489.00619041</v>
+        <v>486.8765500275</v>
       </c>
       <c r="Q14">
-        <v>665.00619041</v>
+        <v>662.8765500275</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1138640105743933</v>
+        <v>0.1144358052967003</v>
       </c>
       <c r="T14">
-        <v>1.052928596636551</v>
+        <v>1.061774079138127</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>20.13492822655001</v>
+        <v>18.58608759373847</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1041691456081293</v>
+        <v>0.1038825819107924</v>
       </c>
       <c r="C15">
-        <v>4890.005591142891</v>
+        <v>4856.538062953709</v>
       </c>
       <c r="D15">
-        <v>5388.920591142891</v>
+        <v>5415.508062953709</v>
       </c>
       <c r="E15">
-        <v>-1827.585</v>
+        <v>-1767.53</v>
       </c>
       <c r="F15">
-        <v>780.715</v>
+        <v>840.7700000000001</v>
       </c>
       <c r="G15">
         <v>281.8</v>
@@ -2523,28 +2523,28 @@
         <v>729.875</v>
       </c>
       <c r="M15">
-        <v>39.2699645</v>
+        <v>42.290731</v>
       </c>
       <c r="N15">
-        <v>690.6050355</v>
+        <v>687.5842689999999</v>
       </c>
       <c r="O15">
-        <v>203.7284854725</v>
+        <v>202.837359355</v>
       </c>
       <c r="P15">
-        <v>486.8765500275</v>
+        <v>484.746909645</v>
       </c>
       <c r="Q15">
-        <v>662.8765500275</v>
+        <v>660.746909645</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1144358052967003</v>
+        <v>0.1150208975706888</v>
       </c>
       <c r="T15">
-        <v>1.061774079138127</v>
+        <v>1.070825270535088</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>18.58608759373847</v>
+        <v>17.25850990847143</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1038825819107924</v>
+        <v>0.1035960182134556</v>
       </c>
       <c r="C16">
-        <v>4856.538062953709</v>
+        <v>4823.33418629141</v>
       </c>
       <c r="D16">
-        <v>5415.508062953709</v>
+        <v>5442.35918629141</v>
       </c>
       <c r="E16">
-        <v>-1767.53</v>
+        <v>-1707.475</v>
       </c>
       <c r="F16">
-        <v>840.7700000000001</v>
+        <v>900.8250000000002</v>
       </c>
       <c r="G16">
         <v>281.8</v>
@@ -2605,28 +2605,28 @@
         <v>729.875</v>
       </c>
       <c r="M16">
-        <v>42.290731</v>
+        <v>45.31149750000001</v>
       </c>
       <c r="N16">
-        <v>687.5842689999999</v>
+        <v>684.5635025</v>
       </c>
       <c r="O16">
-        <v>202.837359355</v>
+        <v>201.9462332375</v>
       </c>
       <c r="P16">
-        <v>484.746909645</v>
+        <v>482.6172692625</v>
       </c>
       <c r="Q16">
-        <v>660.746909645</v>
+        <v>658.6172692625</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1150208975706888</v>
+        <v>0.1156197567217124</v>
       </c>
       <c r="T16">
-        <v>1.070825270535088</v>
+        <v>1.08008943114139</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>17.25850990847143</v>
+        <v>16.10794258124</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1035960182134556</v>
+        <v>0.1033094545161187</v>
       </c>
       <c r="C17">
-        <v>4823.33418629141</v>
+        <v>4790.397902401328</v>
       </c>
       <c r="D17">
-        <v>5442.35918629141</v>
+        <v>5469.477902401328</v>
       </c>
       <c r="E17">
-        <v>-1707.475</v>
+        <v>-1647.42</v>
       </c>
       <c r="F17">
-        <v>900.8249999999999</v>
+        <v>960.88</v>
       </c>
       <c r="G17">
         <v>281.8</v>
@@ -2687,28 +2687,28 @@
         <v>729.875</v>
       </c>
       <c r="M17">
-        <v>45.31149749999999</v>
+        <v>48.332264</v>
       </c>
       <c r="N17">
-        <v>684.5635025</v>
+        <v>681.542736</v>
       </c>
       <c r="O17">
-        <v>201.9462332375</v>
+        <v>201.05510712</v>
       </c>
       <c r="P17">
-        <v>482.6172692625</v>
+        <v>480.48762888</v>
       </c>
       <c r="Q17">
-        <v>658.6172692625</v>
+        <v>656.48762888</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1156197567217124</v>
+        <v>0.1162328744239508</v>
       </c>
       <c r="T17">
-        <v>1.08008943114139</v>
+        <v>1.089574167000223</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>16.10794258124001</v>
+        <v>15.10119616991251</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1033094545161187</v>
+        <v>0.1030228908187819</v>
       </c>
       <c r="C18">
-        <v>4790.397902401328</v>
+        <v>4757.733231477465</v>
       </c>
       <c r="D18">
-        <v>5469.477902401328</v>
+        <v>5496.868231477465</v>
       </c>
       <c r="E18">
-        <v>-1647.42</v>
+        <v>-1587.365</v>
       </c>
       <c r="F18">
-        <v>960.88</v>
+        <v>1020.935</v>
       </c>
       <c r="G18">
         <v>281.8</v>
@@ -2769,28 +2769,28 @@
         <v>729.875</v>
       </c>
       <c r="M18">
-        <v>48.332264</v>
+        <v>51.3530305</v>
       </c>
       <c r="N18">
-        <v>681.542736</v>
+        <v>678.5219695</v>
       </c>
       <c r="O18">
-        <v>201.05510712</v>
+        <v>200.1639810025</v>
       </c>
       <c r="P18">
-        <v>480.48762888</v>
+        <v>478.3579884974999</v>
       </c>
       <c r="Q18">
-        <v>656.48762888</v>
+        <v>654.3579884974999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1162328744239508</v>
+        <v>0.1168607660467251</v>
       </c>
       <c r="T18">
-        <v>1.089574167000223</v>
+        <v>1.099287450711076</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>15.10119616991251</v>
+        <v>14.21289051285883</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1030228908187819</v>
+        <v>0.102736327121445</v>
       </c>
       <c r="C19">
-        <v>4757.733231477465</v>
+        <v>4725.344274649267</v>
       </c>
       <c r="D19">
-        <v>5496.868231477465</v>
+        <v>5524.534274649267</v>
       </c>
       <c r="E19">
-        <v>-1587.365</v>
+        <v>-1527.31</v>
       </c>
       <c r="F19">
-        <v>1020.935</v>
+        <v>1080.99</v>
       </c>
       <c r="G19">
         <v>281.8</v>
@@ -2851,28 +2851,28 @@
         <v>729.875</v>
       </c>
       <c r="M19">
-        <v>51.3530305</v>
+        <v>54.37379700000001</v>
       </c>
       <c r="N19">
-        <v>678.5219695</v>
+        <v>675.501203</v>
       </c>
       <c r="O19">
-        <v>200.1639810025</v>
+        <v>199.272854885</v>
       </c>
       <c r="P19">
-        <v>478.3579884974999</v>
+        <v>476.228348115</v>
       </c>
       <c r="Q19">
-        <v>654.3579884974999</v>
+        <v>652.228348115</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1168607660467251</v>
+        <v>0.1175039720993232</v>
       </c>
       <c r="T19">
-        <v>1.099287450711076</v>
+        <v>1.109237643780731</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>14.21289051285883</v>
+        <v>13.42328548436667</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.102736327121445</v>
+        <v>0.1026506884241082</v>
       </c>
       <c r="C20">
-        <v>4725.344274649266</v>
+        <v>4673.611318441318</v>
       </c>
       <c r="D20">
-        <v>5524.534274649265</v>
+        <v>5532.856318441318</v>
       </c>
       <c r="E20">
-        <v>-1527.31</v>
+        <v>-1467.255</v>
       </c>
       <c r="F20">
-        <v>1080.99</v>
+        <v>1141.045</v>
       </c>
       <c r="G20">
         <v>281.8</v>
@@ -2933,45 +2933,45 @@
         <v>729.875</v>
       </c>
       <c r="M20">
-        <v>54.373797</v>
+        <v>59.106131</v>
       </c>
       <c r="N20">
-        <v>675.501203</v>
+        <v>670.768869</v>
       </c>
       <c r="O20">
-        <v>199.272854885</v>
+        <v>197.876816355</v>
       </c>
       <c r="P20">
-        <v>476.228348115</v>
+        <v>472.892052645</v>
       </c>
       <c r="Q20">
-        <v>652.228348115</v>
+        <v>648.892052645</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1175039720993232</v>
+        <v>0.1181630597828496</v>
       </c>
       <c r="T20">
-        <v>1.109237643780731</v>
+        <v>1.119433520629882</v>
       </c>
       <c r="U20">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V20">
         <v>0.295</v>
       </c>
       <c r="W20">
-        <v>0.0354615</v>
+        <v>0.036519</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y20">
-        <v>13.42328548436667</v>
+        <v>12.34854976381384</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1026506884241082</v>
+        <v>0.1023746997267713</v>
       </c>
       <c r="C21">
-        <v>4673.611318441318</v>
+        <v>4640.547284637397</v>
       </c>
       <c r="D21">
-        <v>5532.856318441318</v>
+        <v>5559.847284637397</v>
       </c>
       <c r="E21">
-        <v>-1467.255</v>
+        <v>-1407.2</v>
       </c>
       <c r="F21">
-        <v>1141.045</v>
+        <v>1201.1</v>
       </c>
       <c r="G21">
         <v>281.8</v>
@@ -3015,28 +3015,28 @@
         <v>729.875</v>
       </c>
       <c r="M21">
-        <v>59.106131</v>
+        <v>62.21698000000001</v>
       </c>
       <c r="N21">
-        <v>670.768869</v>
+        <v>667.65802</v>
       </c>
       <c r="O21">
-        <v>197.876816355</v>
+        <v>196.9591159</v>
       </c>
       <c r="P21">
-        <v>472.892052645</v>
+        <v>470.6989041</v>
       </c>
       <c r="Q21">
-        <v>648.892052645</v>
+        <v>646.6989040999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1181630597828496</v>
+        <v>0.1188386246584641</v>
       </c>
       <c r="T21">
-        <v>1.119433520629882</v>
+        <v>1.129884294400263</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>12.34854976381384</v>
+        <v>11.73112227562315</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1023746997267713</v>
+        <v>0.1020987110294345</v>
       </c>
       <c r="C22">
-        <v>4640.547284637397</v>
+        <v>4607.747882170999</v>
       </c>
       <c r="D22">
-        <v>5559.847284637397</v>
+        <v>5587.102882170999</v>
       </c>
       <c r="E22">
-        <v>-1407.2</v>
+        <v>-1347.145</v>
       </c>
       <c r="F22">
-        <v>1201.1</v>
+        <v>1261.155</v>
       </c>
       <c r="G22">
         <v>281.8</v>
@@ -3097,28 +3097,28 @@
         <v>729.875</v>
       </c>
       <c r="M22">
-        <v>62.21698000000001</v>
+        <v>65.32782900000001</v>
       </c>
       <c r="N22">
-        <v>667.65802</v>
+        <v>664.5471709999999</v>
       </c>
       <c r="O22">
-        <v>196.9591159</v>
+        <v>196.041415445</v>
       </c>
       <c r="P22">
-        <v>470.6989041</v>
+        <v>468.505755555</v>
       </c>
       <c r="Q22">
-        <v>646.6989040999999</v>
+        <v>644.505755555</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1188386246584641</v>
+        <v>0.1195312924423221</v>
       </c>
       <c r="T22">
-        <v>1.129884294400263</v>
+        <v>1.140599644721793</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.73112227562315</v>
+        <v>11.17249740535538</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1020987110294345</v>
+        <v>0.1018227223320976</v>
       </c>
       <c r="C23">
-        <v>4607.747882170999</v>
+        <v>4575.217022058322</v>
       </c>
       <c r="D23">
-        <v>5587.102882170999</v>
+        <v>5614.627022058322</v>
       </c>
       <c r="E23">
-        <v>-1347.145</v>
+        <v>-1287.09</v>
       </c>
       <c r="F23">
-        <v>1261.155</v>
+        <v>1321.21</v>
       </c>
       <c r="G23">
         <v>281.8</v>
@@ -3179,28 +3179,28 @@
         <v>729.875</v>
       </c>
       <c r="M23">
-        <v>65.32782899999999</v>
+        <v>68.438678</v>
       </c>
       <c r="N23">
-        <v>664.547171</v>
+        <v>661.436322</v>
       </c>
       <c r="O23">
-        <v>196.041415445</v>
+        <v>195.12371499</v>
       </c>
       <c r="P23">
-        <v>468.5057555550001</v>
+        <v>466.31260701</v>
       </c>
       <c r="Q23">
-        <v>644.5057555550001</v>
+        <v>642.31260701</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1195312924423221</v>
+        <v>0.1202417209385867</v>
       </c>
       <c r="T23">
-        <v>1.140599644721793</v>
+        <v>1.151589747615669</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.17249740535538</v>
+        <v>10.66465661420286</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1018227223320976</v>
+        <v>0.1015467336347608</v>
       </c>
       <c r="C24">
-        <v>4575.217022058322</v>
+        <v>4542.95869276557</v>
       </c>
       <c r="D24">
-        <v>5614.627022058322</v>
+        <v>5642.42369276557</v>
       </c>
       <c r="E24">
-        <v>-1287.09</v>
+        <v>-1227.035</v>
       </c>
       <c r="F24">
-        <v>1321.21</v>
+        <v>1381.265</v>
       </c>
       <c r="G24">
         <v>281.8</v>
@@ -3261,28 +3261,28 @@
         <v>729.875</v>
       </c>
       <c r="M24">
-        <v>68.438678</v>
+        <v>71.549527</v>
       </c>
       <c r="N24">
-        <v>661.436322</v>
+        <v>658.325473</v>
       </c>
       <c r="O24">
-        <v>195.12371499</v>
+        <v>194.206014535</v>
       </c>
       <c r="P24">
-        <v>466.31260701</v>
+        <v>464.119458465</v>
       </c>
       <c r="Q24">
-        <v>642.31260701</v>
+        <v>640.119458465</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1202417209385867</v>
+        <v>0.1209706021230659</v>
       </c>
       <c r="T24">
-        <v>1.151589747615669</v>
+        <v>1.162865307727568</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.66465661420286</v>
+        <v>10.20097589184622</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1015467336347608</v>
+        <v>0.1015583849374239</v>
       </c>
       <c r="C25">
-        <v>4542.95869276557</v>
+        <v>4481.724648819591</v>
       </c>
       <c r="D25">
-        <v>5642.42369276557</v>
+        <v>5641.24464881959</v>
       </c>
       <c r="E25">
-        <v>-1227.035</v>
+        <v>-1166.98</v>
       </c>
       <c r="F25">
-        <v>1381.265</v>
+        <v>1441.32</v>
       </c>
       <c r="G25">
         <v>281.8</v>
@@ -3343,45 +3343,45 @@
         <v>729.875</v>
       </c>
       <c r="M25">
-        <v>71.549527</v>
+        <v>77.11062000000001</v>
       </c>
       <c r="N25">
-        <v>658.325473</v>
+        <v>652.76438</v>
       </c>
       <c r="O25">
-        <v>194.206014535</v>
+        <v>192.5654921</v>
       </c>
       <c r="P25">
-        <v>464.119458465</v>
+        <v>460.1988879</v>
       </c>
       <c r="Q25">
-        <v>640.119458465</v>
+        <v>636.1988879</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1209706021230659</v>
+        <v>0.1217186643913473</v>
       </c>
       <c r="T25">
-        <v>1.162865307727568</v>
+        <v>1.17443759310557</v>
       </c>
       <c r="U25">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V25">
         <v>0.295</v>
       </c>
       <c r="W25">
-        <v>0.036519</v>
+        <v>0.0377175</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>10.20097589184622</v>
+        <v>9.465298035471637</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1015583849374239</v>
+        <v>0.1012943812400871</v>
       </c>
       <c r="C26">
-        <v>4481.724648819591</v>
+        <v>4448.506770192776</v>
       </c>
       <c r="D26">
-        <v>5641.24464881959</v>
+        <v>5668.081770192776</v>
       </c>
       <c r="E26">
-        <v>-1166.98</v>
+        <v>-1106.925</v>
       </c>
       <c r="F26">
-        <v>1441.32</v>
+        <v>1501.375</v>
       </c>
       <c r="G26">
         <v>281.8</v>
@@ -3425,28 +3425,28 @@
         <v>729.875</v>
       </c>
       <c r="M26">
-        <v>77.11062</v>
+        <v>80.32356249999999</v>
       </c>
       <c r="N26">
-        <v>652.76438</v>
+        <v>649.5514375</v>
       </c>
       <c r="O26">
-        <v>192.5654921</v>
+        <v>191.6176740625</v>
       </c>
       <c r="P26">
-        <v>460.1988879</v>
+        <v>457.9337634375</v>
       </c>
       <c r="Q26">
-        <v>636.1988879</v>
+        <v>633.9337634375</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1217186643913473</v>
+        <v>0.1224866749867828</v>
       </c>
       <c r="T26">
-        <v>1.17443759310557</v>
+        <v>1.186318472760319</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>9.465298035471637</v>
+        <v>9.086686114052773</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1012943812400871</v>
+        <v>0.1010303775427502</v>
       </c>
       <c r="C27">
-        <v>4448.506770192776</v>
+        <v>4415.545456868741</v>
       </c>
       <c r="D27">
-        <v>5668.081770192776</v>
+        <v>5695.175456868741</v>
       </c>
       <c r="E27">
-        <v>-1106.925</v>
+        <v>-1046.87</v>
       </c>
       <c r="F27">
-        <v>1501.375</v>
+        <v>1561.43</v>
       </c>
       <c r="G27">
         <v>281.8</v>
@@ -3507,28 +3507,28 @@
         <v>729.875</v>
       </c>
       <c r="M27">
-        <v>80.32356249999999</v>
+        <v>83.53650500000001</v>
       </c>
       <c r="N27">
-        <v>649.5514375</v>
+        <v>646.338495</v>
       </c>
       <c r="O27">
-        <v>191.6176740625</v>
+        <v>190.669856025</v>
       </c>
       <c r="P27">
-        <v>457.9337634375</v>
+        <v>455.668638975</v>
       </c>
       <c r="Q27">
-        <v>633.9337634375</v>
+        <v>631.668638975</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1224866749867828</v>
+        <v>0.1232754426253381</v>
       </c>
       <c r="T27">
-        <v>1.186318472760319</v>
+        <v>1.198520457270601</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>9.086686114052773</v>
+        <v>8.737198186589204</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1010303775427502</v>
+        <v>0.1007663738454134</v>
       </c>
       <c r="C28">
-        <v>4415.545456868741</v>
+        <v>4382.844405699785</v>
       </c>
       <c r="D28">
-        <v>5695.175456868741</v>
+        <v>5722.529405699785</v>
       </c>
       <c r="E28">
-        <v>-1046.87</v>
+        <v>-986.8150000000001</v>
       </c>
       <c r="F28">
-        <v>1561.43</v>
+        <v>1621.485</v>
       </c>
       <c r="G28">
         <v>281.8</v>
@@ -3589,28 +3589,28 @@
         <v>729.875</v>
       </c>
       <c r="M28">
-        <v>83.53650500000001</v>
+        <v>86.7494475</v>
       </c>
       <c r="N28">
-        <v>646.338495</v>
+        <v>643.1255525</v>
       </c>
       <c r="O28">
-        <v>190.669856025</v>
+        <v>189.7220379875</v>
       </c>
       <c r="P28">
-        <v>455.668638975</v>
+        <v>453.4035145125</v>
       </c>
       <c r="Q28">
-        <v>631.668638975</v>
+        <v>629.4035145125</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1232754426253381</v>
+        <v>0.1240858203361827</v>
       </c>
       <c r="T28">
-        <v>1.198520457270601</v>
+        <v>1.21105674272637</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.737198186589204</v>
+        <v>8.413598253752568</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1007663738454134</v>
+        <v>0.1005023701480765</v>
       </c>
       <c r="C29">
-        <v>4382.844405699785</v>
+        <v>4350.407384904965</v>
       </c>
       <c r="D29">
-        <v>5722.529405699785</v>
+        <v>5750.147384904964</v>
       </c>
       <c r="E29">
-        <v>-986.8150000000001</v>
+        <v>-926.76</v>
       </c>
       <c r="F29">
-        <v>1621.485</v>
+        <v>1681.54</v>
       </c>
       <c r="G29">
         <v>281.8</v>
@@ -3671,28 +3671,28 @@
         <v>729.875</v>
       </c>
       <c r="M29">
-        <v>86.7494475</v>
+        <v>89.96239000000001</v>
       </c>
       <c r="N29">
-        <v>643.1255525</v>
+        <v>639.91261</v>
       </c>
       <c r="O29">
-        <v>189.7220379875</v>
+        <v>188.77421995</v>
       </c>
       <c r="P29">
-        <v>453.4035145125</v>
+        <v>451.13839005</v>
       </c>
       <c r="Q29">
-        <v>629.4035145125</v>
+        <v>627.13839005</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1240858203361827</v>
+        <v>0.1249187085389951</v>
       </c>
       <c r="T29">
-        <v>1.21105674272637</v>
+        <v>1.223941258333689</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.413598253752568</v>
+        <v>8.113112601832832</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1005023701480765</v>
+        <v>0.1002383664507397</v>
       </c>
       <c r="C30">
-        <v>4350.407384904965</v>
+        <v>4318.238235800589</v>
       </c>
       <c r="D30">
-        <v>5750.147384904964</v>
+        <v>5778.033235800589</v>
       </c>
       <c r="E30">
-        <v>-926.76</v>
+        <v>-866.7049999999999</v>
       </c>
       <c r="F30">
-        <v>1681.54</v>
+        <v>1741.595</v>
       </c>
       <c r="G30">
         <v>281.8</v>
@@ -3753,28 +3753,28 @@
         <v>729.875</v>
       </c>
       <c r="M30">
-        <v>89.96239000000001</v>
+        <v>93.17533250000001</v>
       </c>
       <c r="N30">
-        <v>639.91261</v>
+        <v>636.6996675</v>
       </c>
       <c r="O30">
-        <v>188.77421995</v>
+        <v>187.8264019125</v>
       </c>
       <c r="P30">
-        <v>451.13839005</v>
+        <v>448.8732655875</v>
       </c>
       <c r="Q30">
-        <v>627.13839005</v>
+        <v>624.8732655875001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1249187085389951</v>
+        <v>0.1257750583813235</v>
       </c>
       <c r="T30">
-        <v>1.223941258333689</v>
+        <v>1.237188718042622</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.113112601832832</v>
+        <v>7.833350098321355</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1002383664507397</v>
+        <v>0.1001435627534028</v>
       </c>
       <c r="C31">
-        <v>4318.238235800589</v>
+        <v>4268.263158542769</v>
       </c>
       <c r="D31">
-        <v>5778.033235800589</v>
+        <v>5788.113158542768</v>
       </c>
       <c r="E31">
-        <v>-866.7050000000004</v>
+        <v>-806.6500000000003</v>
       </c>
       <c r="F31">
-        <v>1741.595</v>
+        <v>1801.65</v>
       </c>
       <c r="G31">
         <v>281.8</v>
@@ -3835,45 +3835,45 @@
         <v>729.875</v>
       </c>
       <c r="M31">
-        <v>93.17533249999998</v>
+        <v>97.829595</v>
       </c>
       <c r="N31">
-        <v>636.6996675</v>
+        <v>632.045405</v>
       </c>
       <c r="O31">
-        <v>187.8264019125</v>
+        <v>186.453394475</v>
       </c>
       <c r="P31">
-        <v>448.8732655875</v>
+        <v>445.592010525</v>
       </c>
       <c r="Q31">
-        <v>624.8732655875001</v>
+        <v>621.592010525</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1257750583813235</v>
+        <v>0.126655875362004</v>
       </c>
       <c r="T31">
-        <v>1.237188718042622</v>
+        <v>1.250814676600382</v>
       </c>
       <c r="U31">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V31">
         <v>0.295</v>
       </c>
       <c r="W31">
-        <v>0.0377175</v>
+        <v>0.0382815</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y31">
-        <v>7.833350098321358</v>
+        <v>7.460676904570646</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1001435627534028</v>
+        <v>0.09988519905606597</v>
       </c>
       <c r="C32">
-        <v>4268.263158542769</v>
+        <v>4235.857836131918</v>
       </c>
       <c r="D32">
-        <v>5788.113158542768</v>
+        <v>5815.762836131918</v>
       </c>
       <c r="E32">
-        <v>-806.6500000000003</v>
+        <v>-746.5950000000003</v>
       </c>
       <c r="F32">
-        <v>1801.65</v>
+        <v>1861.705</v>
       </c>
       <c r="G32">
         <v>281.8</v>
@@ -3917,28 +3917,28 @@
         <v>729.875</v>
       </c>
       <c r="M32">
-        <v>97.829595</v>
+        <v>101.0905815</v>
       </c>
       <c r="N32">
-        <v>632.045405</v>
+        <v>628.7844185</v>
       </c>
       <c r="O32">
-        <v>186.453394475</v>
+        <v>185.4914034575</v>
       </c>
       <c r="P32">
-        <v>445.592010525</v>
+        <v>443.2930150425</v>
       </c>
       <c r="Q32">
-        <v>621.592010525</v>
+        <v>619.2930150425</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.126655875362004</v>
+        <v>0.1275622232696608</v>
       </c>
       <c r="T32">
-        <v>1.250814676600382</v>
+        <v>1.264835590478657</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.460676904570646</v>
+        <v>7.220009907649013</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09988519905606597</v>
+        <v>0.0996268353587291</v>
       </c>
       <c r="C33">
-        <v>4235.857836131918</v>
+        <v>4203.717945373681</v>
       </c>
       <c r="D33">
-        <v>5815.762836131918</v>
+        <v>5843.677945373681</v>
       </c>
       <c r="E33">
-        <v>-746.5950000000003</v>
+        <v>-686.5400000000002</v>
       </c>
       <c r="F33">
-        <v>1861.705</v>
+        <v>1921.76</v>
       </c>
       <c r="G33">
         <v>281.8</v>
@@ -3999,28 +3999,28 @@
         <v>729.875</v>
       </c>
       <c r="M33">
-        <v>101.0905815</v>
+        <v>104.351568</v>
       </c>
       <c r="N33">
-        <v>628.7844185</v>
+        <v>625.523432</v>
       </c>
       <c r="O33">
-        <v>185.4914034575</v>
+        <v>184.52941244</v>
       </c>
       <c r="P33">
-        <v>443.2930150425</v>
+        <v>440.99401956</v>
       </c>
       <c r="Q33">
-        <v>619.2930150425</v>
+        <v>616.99401956</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1275622232696608</v>
+        <v>0.1284952284687193</v>
       </c>
       <c r="T33">
-        <v>1.264835590478657</v>
+        <v>1.279268884176881</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.220009907649013</v>
+        <v>6.994384598034981</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0996268353587291</v>
+        <v>0.09936847166139226</v>
       </c>
       <c r="C34">
-        <v>4203.717945373681</v>
+        <v>4171.847326842615</v>
       </c>
       <c r="D34">
-        <v>5843.677945373681</v>
+        <v>5871.862326842615</v>
       </c>
       <c r="E34">
-        <v>-686.5400000000002</v>
+        <v>-626.4850000000001</v>
       </c>
       <c r="F34">
-        <v>1921.76</v>
+        <v>1981.815</v>
       </c>
       <c r="G34">
         <v>281.8</v>
@@ -4081,28 +4081,28 @@
         <v>729.875</v>
       </c>
       <c r="M34">
-        <v>104.351568</v>
+        <v>107.6125545</v>
       </c>
       <c r="N34">
-        <v>625.523432</v>
+        <v>622.2624455</v>
       </c>
       <c r="O34">
-        <v>184.52941244</v>
+        <v>183.5674214225</v>
       </c>
       <c r="P34">
-        <v>440.99401956</v>
+        <v>438.6950240775</v>
       </c>
       <c r="Q34">
-        <v>616.99401956</v>
+        <v>614.6950240775</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1284952284687193</v>
+        <v>0.1294560845692422</v>
       </c>
       <c r="T34">
-        <v>1.279268884176881</v>
+        <v>1.294133022463111</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.994384598034981</v>
+        <v>6.782433549609679</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09936847166139226</v>
+        <v>0.09911010796405541</v>
       </c>
       <c r="C35">
-        <v>4171.847326842615</v>
+        <v>4140.249895565586</v>
       </c>
       <c r="D35">
-        <v>5871.862326842615</v>
+        <v>5900.319895565585</v>
       </c>
       <c r="E35">
-        <v>-626.4850000000001</v>
+        <v>-566.4300000000001</v>
       </c>
       <c r="F35">
-        <v>1981.815</v>
+        <v>2041.87</v>
       </c>
       <c r="G35">
         <v>281.8</v>
@@ -4163,28 +4163,28 @@
         <v>729.875</v>
       </c>
       <c r="M35">
-        <v>107.6125545</v>
+        <v>110.873541</v>
       </c>
       <c r="N35">
-        <v>622.2624455</v>
+        <v>619.001459</v>
       </c>
       <c r="O35">
-        <v>183.5674214225</v>
+        <v>182.605430405</v>
       </c>
       <c r="P35">
-        <v>438.6950240775</v>
+        <v>436.396028595</v>
       </c>
       <c r="Q35">
-        <v>614.6950240775</v>
+        <v>612.396028595</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1294560845692422</v>
+        <v>0.1304460575212961</v>
       </c>
       <c r="T35">
-        <v>1.294133022463111</v>
+        <v>1.309447589182258</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.782433549609679</v>
+        <v>6.582950209915276</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09911010796405541</v>
+        <v>0.09885174426671856</v>
       </c>
       <c r="C36">
-        <v>4140.249895565586</v>
+        <v>4108.929642834674</v>
       </c>
       <c r="D36">
-        <v>5900.319895565585</v>
+        <v>5929.054642834674</v>
       </c>
       <c r="E36">
-        <v>-566.4300000000001</v>
+        <v>-506.375</v>
       </c>
       <c r="F36">
-        <v>2041.87</v>
+        <v>2101.925</v>
       </c>
       <c r="G36">
         <v>281.8</v>
@@ -4245,28 +4245,28 @@
         <v>729.875</v>
       </c>
       <c r="M36">
-        <v>110.873541</v>
+        <v>114.1345275</v>
       </c>
       <c r="N36">
-        <v>619.001459</v>
+        <v>615.7404725</v>
       </c>
       <c r="O36">
-        <v>182.605430405</v>
+        <v>181.6434393875</v>
       </c>
       <c r="P36">
-        <v>436.396028595</v>
+        <v>434.0970331125</v>
       </c>
       <c r="Q36">
-        <v>612.396028595</v>
+        <v>610.0970331125</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1304460575212961</v>
+        <v>0.131466491179567</v>
       </c>
       <c r="T36">
-        <v>1.309447589182258</v>
+        <v>1.325233373338917</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.582950209915276</v>
+        <v>6.39486591820341</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09885174426671856</v>
+        <v>0.0985933805693817</v>
       </c>
       <c r="C37">
-        <v>4108.929642834674</v>
+        <v>4077.890638073354</v>
       </c>
       <c r="D37">
-        <v>5929.054642834674</v>
+        <v>5958.070638073355</v>
       </c>
       <c r="E37">
-        <v>-506.375</v>
+        <v>-446.3199999999997</v>
       </c>
       <c r="F37">
-        <v>2101.925</v>
+        <v>2161.98</v>
       </c>
       <c r="G37">
         <v>281.8</v>
@@ -4327,28 +4327,28 @@
         <v>729.875</v>
       </c>
       <c r="M37">
-        <v>114.1345275</v>
+        <v>117.395514</v>
       </c>
       <c r="N37">
-        <v>615.7404725</v>
+        <v>612.479486</v>
       </c>
       <c r="O37">
-        <v>181.6434393875</v>
+        <v>180.68144837</v>
       </c>
       <c r="P37">
-        <v>434.0970331125</v>
+        <v>431.79803763</v>
       </c>
       <c r="Q37">
-        <v>610.0970331125</v>
+        <v>607.79803763</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.131466491179567</v>
+        <v>0.1325188133896589</v>
       </c>
       <c r="T37">
-        <v>1.325233373338917</v>
+        <v>1.341512463250472</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.39486591820341</v>
+        <v>6.21723075380887</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09859338056938172</v>
+        <v>0.09859586687204488</v>
       </c>
       <c r="C38">
-        <v>4077.890638073354</v>
+        <v>4017.555056130628</v>
       </c>
       <c r="D38">
-        <v>5958.070638073354</v>
+        <v>5957.790056130628</v>
       </c>
       <c r="E38">
-        <v>-446.3200000000002</v>
+        <v>-386.2650000000003</v>
       </c>
       <c r="F38">
-        <v>2161.98</v>
+        <v>2222.035</v>
       </c>
       <c r="G38">
         <v>281.8</v>
@@ -4409,45 +4409,45 @@
         <v>729.875</v>
       </c>
       <c r="M38">
-        <v>117.395514</v>
+        <v>122.8785355</v>
       </c>
       <c r="N38">
-        <v>612.479486</v>
+        <v>606.9964645</v>
       </c>
       <c r="O38">
-        <v>180.68144837</v>
+        <v>179.0639570275</v>
       </c>
       <c r="P38">
-        <v>431.79803763</v>
+        <v>427.9325074725</v>
       </c>
       <c r="Q38">
-        <v>607.79803763</v>
+        <v>603.9325074725</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1325188133896589</v>
+        <v>0.1336045426540395</v>
       </c>
       <c r="T38">
-        <v>1.341512463250472</v>
+        <v>1.358308349667155</v>
       </c>
       <c r="U38">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V38">
         <v>0.295</v>
       </c>
       <c r="W38">
-        <v>0.0382815</v>
+        <v>0.03898650000000001</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y38">
-        <v>6.217230753808871</v>
+        <v>5.939808747150962</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09859586687204488</v>
+        <v>0.09834455317470803</v>
       </c>
       <c r="C39">
-        <v>4017.555056130628</v>
+        <v>3985.99538355276</v>
       </c>
       <c r="D39">
-        <v>5957.790056130628</v>
+        <v>5986.28538355276</v>
       </c>
       <c r="E39">
-        <v>-386.2650000000003</v>
+        <v>-326.21</v>
       </c>
       <c r="F39">
-        <v>2222.035</v>
+        <v>2282.09</v>
       </c>
       <c r="G39">
         <v>281.8</v>
@@ -4491,28 +4491,28 @@
         <v>729.875</v>
       </c>
       <c r="M39">
-        <v>122.8785355</v>
+        <v>126.199577</v>
       </c>
       <c r="N39">
-        <v>606.9964645</v>
+        <v>603.675423</v>
       </c>
       <c r="O39">
-        <v>179.0639570275</v>
+        <v>178.084249785</v>
       </c>
       <c r="P39">
-        <v>427.9325074725</v>
+        <v>425.591173215</v>
       </c>
       <c r="Q39">
-        <v>603.9325074725</v>
+        <v>601.591173215</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1336045426540395</v>
+        <v>0.1347252954430775</v>
       </c>
       <c r="T39">
-        <v>1.358308349667155</v>
+        <v>1.375646038871473</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.939808747150962</v>
+        <v>5.783497990646989</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09834455317470803</v>
+        <v>0.09809323947737117</v>
       </c>
       <c r="C40">
-        <v>3985.99538355276</v>
+        <v>3954.709599766747</v>
       </c>
       <c r="D40">
-        <v>5986.28538355276</v>
+        <v>6015.054599766747</v>
       </c>
       <c r="E40">
-        <v>-326.21</v>
+        <v>-266.1550000000002</v>
       </c>
       <c r="F40">
-        <v>2282.09</v>
+        <v>2342.145</v>
       </c>
       <c r="G40">
         <v>281.8</v>
@@ -4573,28 +4573,28 @@
         <v>729.875</v>
       </c>
       <c r="M40">
-        <v>126.199577</v>
+        <v>129.5206185</v>
       </c>
       <c r="N40">
-        <v>603.675423</v>
+        <v>600.3543815</v>
       </c>
       <c r="O40">
-        <v>178.084249785</v>
+        <v>177.1045425425</v>
       </c>
       <c r="P40">
-        <v>425.591173215</v>
+        <v>423.2498389575001</v>
       </c>
       <c r="Q40">
-        <v>601.591173215</v>
+        <v>599.2498389575001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1347252954430775</v>
+        <v>0.1358827942251986</v>
       </c>
       <c r="T40">
-        <v>1.375646038871473</v>
+        <v>1.393552176902162</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.783497990646989</v>
+        <v>5.635203170373989</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09809323947737117</v>
+        <v>0.09784192578003431</v>
       </c>
       <c r="C41">
-        <v>3954.709599766747</v>
+        <v>3923.701672650632</v>
       </c>
       <c r="D41">
-        <v>6015.054599766747</v>
+        <v>6044.101672650632</v>
       </c>
       <c r="E41">
-        <v>-266.1550000000002</v>
+        <v>-206.0999999999999</v>
       </c>
       <c r="F41">
-        <v>2342.145</v>
+        <v>2402.2</v>
       </c>
       <c r="G41">
         <v>281.8</v>
@@ -4655,28 +4655,28 @@
         <v>729.875</v>
       </c>
       <c r="M41">
-        <v>129.5206185</v>
+        <v>132.84166</v>
       </c>
       <c r="N41">
-        <v>600.3543815</v>
+        <v>597.03334</v>
       </c>
       <c r="O41">
-        <v>177.1045425425</v>
+        <v>176.1248353</v>
       </c>
       <c r="P41">
-        <v>423.2498389575001</v>
+        <v>420.9085047</v>
       </c>
       <c r="Q41">
-        <v>599.2498389575001</v>
+        <v>596.9085047</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1358827942251986</v>
+        <v>0.1370788763000572</v>
       </c>
       <c r="T41">
-        <v>1.393552176902162</v>
+        <v>1.412055186200541</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.635203170373989</v>
+        <v>5.494323091114639</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09784192578003431</v>
+        <v>0.09759061208269747</v>
       </c>
       <c r="C42">
-        <v>3923.701672650632</v>
+        <v>3892.975647098902</v>
       </c>
       <c r="D42">
-        <v>6044.101672650632</v>
+        <v>6073.430647098902</v>
       </c>
       <c r="E42">
-        <v>-206.0999999999999</v>
+        <v>-146.0450000000001</v>
       </c>
       <c r="F42">
-        <v>2402.2</v>
+        <v>2462.255</v>
       </c>
       <c r="G42">
         <v>281.8</v>
@@ -4737,28 +4737,28 @@
         <v>729.875</v>
       </c>
       <c r="M42">
-        <v>132.84166</v>
+        <v>136.1627015</v>
       </c>
       <c r="N42">
-        <v>597.03334</v>
+        <v>593.7122985</v>
       </c>
       <c r="O42">
-        <v>176.1248353</v>
+        <v>175.1451280575</v>
       </c>
       <c r="P42">
-        <v>420.9085047</v>
+        <v>418.5671704425</v>
       </c>
       <c r="Q42">
-        <v>596.9085047</v>
+        <v>594.5671704425</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1370788763000572</v>
+        <v>0.1383155035299957</v>
       </c>
       <c r="T42">
-        <v>1.412055186200541</v>
+        <v>1.431185416153103</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.494323091114639</v>
+        <v>5.360315210843551</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09759061208269747</v>
+        <v>0.09733929838536062</v>
       </c>
       <c r="C43">
-        <v>3892.975647098902</v>
+        <v>3862.535646900196</v>
       </c>
       <c r="D43">
-        <v>6073.430647098902</v>
+        <v>6103.045646900197</v>
       </c>
       <c r="E43">
-        <v>-146.0450000000001</v>
+        <v>-85.98999999999978</v>
       </c>
       <c r="F43">
-        <v>2462.255</v>
+        <v>2522.31</v>
       </c>
       <c r="G43">
         <v>281.8</v>
@@ -4819,28 +4819,28 @@
         <v>729.875</v>
       </c>
       <c r="M43">
-        <v>136.1627015</v>
+        <v>139.483743</v>
       </c>
       <c r="N43">
-        <v>593.7122985</v>
+        <v>590.391257</v>
       </c>
       <c r="O43">
-        <v>175.1451280575</v>
+        <v>174.165420815</v>
       </c>
       <c r="P43">
-        <v>418.5671704425</v>
+        <v>416.225836185</v>
       </c>
       <c r="Q43">
-        <v>594.5671704425</v>
+        <v>592.225836185</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1383155035299957</v>
+        <v>0.139594773078208</v>
       </c>
       <c r="T43">
-        <v>1.431185416153103</v>
+        <v>1.450975309207476</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.360315210843551</v>
+        <v>5.232688658204418</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09733929838536064</v>
+        <v>0.09708798468802377</v>
       </c>
       <c r="C44">
-        <v>3862.535646900195</v>
+        <v>3832.385876670246</v>
       </c>
       <c r="D44">
-        <v>6103.045646900195</v>
+        <v>6132.950876670246</v>
       </c>
       <c r="E44">
-        <v>-85.99000000000024</v>
+        <v>-25.9350000000004</v>
       </c>
       <c r="F44">
-        <v>2522.31</v>
+        <v>2582.365</v>
       </c>
       <c r="G44">
         <v>281.8</v>
@@ -4901,28 +4901,28 @@
         <v>729.875</v>
       </c>
       <c r="M44">
-        <v>139.483743</v>
+        <v>142.8047845</v>
       </c>
       <c r="N44">
-        <v>590.391257</v>
+        <v>587.0702155</v>
       </c>
       <c r="O44">
-        <v>174.165420815</v>
+        <v>173.1857135725</v>
       </c>
       <c r="P44">
-        <v>416.225836185</v>
+        <v>413.8845019275</v>
       </c>
       <c r="Q44">
-        <v>592.225836185</v>
+        <v>589.8845019275</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.139594773078208</v>
+        <v>0.1409189292772347</v>
       </c>
       <c r="T44">
-        <v>1.450975309207476</v>
+        <v>1.471459584474284</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.232688658204419</v>
+        <v>5.110998224292689</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09708798468802377</v>
+        <v>0.09683667099068693</v>
       </c>
       <c r="C45">
-        <v>3832.385876670246</v>
+        <v>3802.530623841891</v>
       </c>
       <c r="D45">
-        <v>6132.950876670246</v>
+        <v>6163.150623841891</v>
       </c>
       <c r="E45">
-        <v>-25.9350000000004</v>
+        <v>34.11999999999989</v>
       </c>
       <c r="F45">
-        <v>2582.365</v>
+        <v>2642.42</v>
       </c>
       <c r="G45">
         <v>281.8</v>
@@ -4983,28 +4983,28 @@
         <v>729.875</v>
       </c>
       <c r="M45">
-        <v>142.8047845</v>
+        <v>146.125826</v>
       </c>
       <c r="N45">
-        <v>587.0702155</v>
+        <v>583.749174</v>
       </c>
       <c r="O45">
-        <v>173.1857135725</v>
+        <v>172.20600633</v>
       </c>
       <c r="P45">
-        <v>413.8845019275</v>
+        <v>411.54316767</v>
       </c>
       <c r="Q45">
-        <v>589.8845019275</v>
+        <v>587.54316767</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1409189292772347</v>
+        <v>0.1422903767690838</v>
       </c>
       <c r="T45">
-        <v>1.471459584474284</v>
+        <v>1.492675441000621</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.110998224292689</v>
+        <v>4.994839173740582</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09683667099068693</v>
+        <v>0.09658535729335006</v>
       </c>
       <c r="C46">
-        <v>3802.530623841891</v>
+        <v>3772.974260714227</v>
       </c>
       <c r="D46">
-        <v>6163.150623841891</v>
+        <v>6193.649260714226</v>
       </c>
       <c r="E46">
-        <v>34.11999999999989</v>
+        <v>94.17499999999973</v>
       </c>
       <c r="F46">
-        <v>2642.42</v>
+        <v>2702.475</v>
       </c>
       <c r="G46">
         <v>281.8</v>
@@ -5065,28 +5065,28 @@
         <v>729.875</v>
       </c>
       <c r="M46">
-        <v>146.125826</v>
+        <v>149.4468675</v>
       </c>
       <c r="N46">
-        <v>583.749174</v>
+        <v>580.4281324999999</v>
       </c>
       <c r="O46">
-        <v>172.20600633</v>
+        <v>171.2262990875</v>
       </c>
       <c r="P46">
-        <v>411.54316767</v>
+        <v>409.2018334125</v>
       </c>
       <c r="Q46">
-        <v>587.54316767</v>
+        <v>585.2018334125</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1422903767690838</v>
+        <v>0.1437116950788183</v>
       </c>
       <c r="T46">
-        <v>1.492675441000621</v>
+        <v>1.514662783218824</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.994839173740582</v>
+        <v>4.883842747657457</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09658535729335006</v>
+        <v>0.09633404359601323</v>
       </c>
       <c r="C47">
-        <v>3772.974260714227</v>
+        <v>3743.721246562839</v>
       </c>
       <c r="D47">
-        <v>6193.649260714226</v>
+        <v>6224.45124656284</v>
       </c>
       <c r="E47">
-        <v>94.17499999999973</v>
+        <v>154.23</v>
       </c>
       <c r="F47">
-        <v>2702.475</v>
+        <v>2762.53</v>
       </c>
       <c r="G47">
         <v>281.8</v>
@@ -5147,28 +5147,28 @@
         <v>729.875</v>
       </c>
       <c r="M47">
-        <v>149.4468675</v>
+        <v>152.767909</v>
       </c>
       <c r="N47">
-        <v>580.4281324999999</v>
+        <v>577.107091</v>
       </c>
       <c r="O47">
-        <v>171.2262990875</v>
+        <v>170.246591845</v>
       </c>
       <c r="P47">
-        <v>409.2018334125</v>
+        <v>406.860499155</v>
       </c>
       <c r="Q47">
-        <v>585.2018334125</v>
+        <v>582.860499155</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1437116950788183</v>
+        <v>0.1451856548074319</v>
       </c>
       <c r="T47">
-        <v>1.514662783218824</v>
+        <v>1.537464471445109</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.883842747657457</v>
+        <v>4.777672253143164</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09633404359601323</v>
+        <v>0.0960827298986764</v>
       </c>
       <c r="C48">
-        <v>3743.721246562839</v>
+        <v>3714.776129813386</v>
       </c>
       <c r="D48">
-        <v>6224.45124656284</v>
+        <v>6255.561129813386</v>
       </c>
       <c r="E48">
-        <v>154.23</v>
+        <v>214.2849999999999</v>
       </c>
       <c r="F48">
-        <v>2762.53</v>
+        <v>2822.585</v>
       </c>
       <c r="G48">
         <v>281.8</v>
@@ -5229,28 +5229,28 @@
         <v>729.875</v>
       </c>
       <c r="M48">
-        <v>152.767909</v>
+        <v>156.0889505</v>
       </c>
       <c r="N48">
-        <v>577.107091</v>
+        <v>573.7860495</v>
       </c>
       <c r="O48">
-        <v>170.246591845</v>
+        <v>169.2668846025</v>
       </c>
       <c r="P48">
-        <v>406.860499155</v>
+        <v>404.5191648975</v>
       </c>
       <c r="Q48">
-        <v>582.860499155</v>
+        <v>580.5191648975</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1451856548074319</v>
+        <v>0.14671523565788</v>
       </c>
       <c r="T48">
-        <v>1.537464471445109</v>
+        <v>1.561126600736537</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.777672253143164</v>
+        <v>4.676019652012459</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.0960827298986764</v>
+        <v>0.09583141620133953</v>
       </c>
       <c r="C49">
-        <v>3714.776129813386</v>
+        <v>3686.143550280631</v>
       </c>
       <c r="D49">
-        <v>6255.561129813386</v>
+        <v>6286.983550280631</v>
       </c>
       <c r="E49">
-        <v>214.2849999999999</v>
+        <v>274.3400000000001</v>
       </c>
       <c r="F49">
-        <v>2822.585</v>
+        <v>2882.64</v>
       </c>
       <c r="G49">
         <v>281.8</v>
@@ -5311,28 +5311,28 @@
         <v>729.875</v>
       </c>
       <c r="M49">
-        <v>156.0889505</v>
+        <v>159.409992</v>
       </c>
       <c r="N49">
-        <v>573.7860495</v>
+        <v>570.465008</v>
       </c>
       <c r="O49">
-        <v>169.2668846025</v>
+        <v>168.28717736</v>
       </c>
       <c r="P49">
-        <v>404.5191648975</v>
+        <v>402.17783064</v>
       </c>
       <c r="Q49">
-        <v>580.5191648975</v>
+        <v>578.17783064</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.14671523565788</v>
+        <v>0.1483036465410376</v>
       </c>
       <c r="T49">
-        <v>1.561126600736537</v>
+        <v>1.585698811923789</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.676019652012459</v>
+        <v>4.578602575928866</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09583141620133953</v>
+        <v>0.09644372750400268</v>
       </c>
       <c r="C50">
-        <v>3686.143550280631</v>
+        <v>3550.075364102937</v>
       </c>
       <c r="D50">
-        <v>6286.983550280631</v>
+        <v>6210.970364102937</v>
       </c>
       <c r="E50">
-        <v>274.3399999999997</v>
+        <v>334.395</v>
       </c>
       <c r="F50">
-        <v>2882.64</v>
+        <v>2942.695</v>
       </c>
       <c r="G50">
         <v>281.8</v>
@@ -5393,45 +5393,45 @@
         <v>729.875</v>
       </c>
       <c r="M50">
-        <v>159.409992</v>
+        <v>170.087771</v>
       </c>
       <c r="N50">
-        <v>570.465008</v>
+        <v>559.787229</v>
       </c>
       <c r="O50">
-        <v>168.28717736</v>
+        <v>165.137232555</v>
       </c>
       <c r="P50">
-        <v>402.17783064</v>
+        <v>394.6499964450001</v>
       </c>
       <c r="Q50">
-        <v>578.17783064</v>
+        <v>570.6499964450001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1483036465410376</v>
+        <v>0.1499543480470641</v>
       </c>
       <c r="T50">
-        <v>1.585698811923789</v>
+        <v>1.611234639236031</v>
       </c>
       <c r="U50">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V50">
         <v>0.295</v>
       </c>
       <c r="W50">
-        <v>0.03898650000000001</v>
+        <v>0.04074900000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>4.578602575928867</v>
+        <v>4.291166823510197</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09644372750400268</v>
+        <v>0.09621003880666583</v>
       </c>
       <c r="C51">
-        <v>3550.075364102937</v>
+        <v>3518.812914316033</v>
       </c>
       <c r="D51">
-        <v>6210.970364102937</v>
+        <v>6239.762914316033</v>
       </c>
       <c r="E51">
-        <v>334.395</v>
+        <v>394.4499999999998</v>
       </c>
       <c r="F51">
-        <v>2942.695</v>
+        <v>3002.75</v>
       </c>
       <c r="G51">
         <v>281.8</v>
@@ -5475,28 +5475,28 @@
         <v>729.875</v>
       </c>
       <c r="M51">
-        <v>170.087771</v>
+        <v>173.55895</v>
       </c>
       <c r="N51">
-        <v>559.787229</v>
+        <v>556.31605</v>
       </c>
       <c r="O51">
-        <v>165.137232555</v>
+        <v>164.11323475</v>
       </c>
       <c r="P51">
-        <v>394.6499964450001</v>
+        <v>392.20281525</v>
       </c>
       <c r="Q51">
-        <v>570.6499964450001</v>
+        <v>568.20281525</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1499543480470641</v>
+        <v>0.1516710776133317</v>
       </c>
       <c r="T51">
-        <v>1.611234639236031</v>
+        <v>1.637791899640764</v>
       </c>
       <c r="U51">
         <v>0.0578</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.291166823510197</v>
+        <v>4.205343487039994</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09621003880666583</v>
+        <v>0.09597635010932898</v>
       </c>
       <c r="C52">
-        <v>3518.812914316033</v>
+        <v>3487.818658351024</v>
       </c>
       <c r="D52">
-        <v>6239.762914316033</v>
+        <v>6268.823658351023</v>
       </c>
       <c r="E52">
-        <v>394.4499999999998</v>
+        <v>454.5049999999997</v>
       </c>
       <c r="F52">
-        <v>3002.75</v>
+        <v>3062.805</v>
       </c>
       <c r="G52">
         <v>281.8</v>
@@ -5557,28 +5557,28 @@
         <v>729.875</v>
       </c>
       <c r="M52">
-        <v>173.55895</v>
+        <v>177.030129</v>
       </c>
       <c r="N52">
-        <v>556.31605</v>
+        <v>552.844871</v>
       </c>
       <c r="O52">
-        <v>164.11323475</v>
+        <v>163.089236945</v>
       </c>
       <c r="P52">
-        <v>392.20281525</v>
+        <v>389.755634055</v>
       </c>
       <c r="Q52">
-        <v>568.20281525</v>
+        <v>565.755634055</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1516710776133317</v>
+        <v>0.1534578777741408</v>
       </c>
       <c r="T52">
-        <v>1.637791899640764</v>
+        <v>1.665433129857934</v>
       </c>
       <c r="U52">
         <v>0.0578</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.205343487039994</v>
+        <v>4.122885771607837</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09597635010932898</v>
+        <v>0.09574266141199211</v>
       </c>
       <c r="C53">
-        <v>3487.818658351024</v>
+        <v>3457.096360957113</v>
       </c>
       <c r="D53">
-        <v>6268.823658351023</v>
+        <v>6298.156360957113</v>
       </c>
       <c r="E53">
-        <v>454.5049999999997</v>
+        <v>514.5599999999999</v>
       </c>
       <c r="F53">
-        <v>3062.805</v>
+        <v>3122.86</v>
       </c>
       <c r="G53">
         <v>281.8</v>
@@ -5639,28 +5639,28 @@
         <v>729.875</v>
       </c>
       <c r="M53">
-        <v>177.030129</v>
+        <v>180.501308</v>
       </c>
       <c r="N53">
-        <v>552.844871</v>
+        <v>549.373692</v>
       </c>
       <c r="O53">
-        <v>163.089236945</v>
+        <v>162.06523914</v>
       </c>
       <c r="P53">
-        <v>389.755634055</v>
+        <v>387.30845286</v>
       </c>
       <c r="Q53">
-        <v>565.755634055</v>
+        <v>563.30845286</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1534578777741408</v>
+        <v>0.1553191279416503</v>
       </c>
       <c r="T53">
-        <v>1.665433129857934</v>
+        <v>1.69422607800082</v>
       </c>
       <c r="U53">
         <v>0.0578</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.122885771607837</v>
+        <v>4.043599506769224</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09574266141199211</v>
+        <v>0.09681674771465527</v>
       </c>
       <c r="C54">
-        <v>3457.096360957113</v>
+        <v>3264.442483483165</v>
       </c>
       <c r="D54">
-        <v>6298.156360957113</v>
+        <v>6165.557483483165</v>
       </c>
       <c r="E54">
-        <v>514.5599999999999</v>
+        <v>574.6149999999998</v>
       </c>
       <c r="F54">
-        <v>3122.86</v>
+        <v>3182.915</v>
       </c>
       <c r="G54">
         <v>281.8</v>
@@ -5721,45 +5721,45 @@
         <v>729.875</v>
       </c>
       <c r="M54">
-        <v>180.501308</v>
+        <v>195.1126895</v>
       </c>
       <c r="N54">
-        <v>549.373692</v>
+        <v>534.7623105</v>
       </c>
       <c r="O54">
-        <v>162.06523914</v>
+        <v>157.7548815975</v>
       </c>
       <c r="P54">
-        <v>387.30845286</v>
+        <v>377.0074289025</v>
       </c>
       <c r="Q54">
-        <v>563.30845286</v>
+        <v>553.0074289025</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1553191279416503</v>
+        <v>0.1572595802439474</v>
       </c>
       <c r="T54">
-        <v>1.69422607800082</v>
+        <v>1.724244257979573</v>
       </c>
       <c r="U54">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V54">
         <v>0.295</v>
       </c>
       <c r="W54">
-        <v>0.04074900000000001</v>
+        <v>0.0432165</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>4.043599506769224</v>
+        <v>3.740786936361717</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09681674771465527</v>
+        <v>0.09660773401731843</v>
       </c>
       <c r="C55">
-        <v>3264.442483483165</v>
+        <v>3229.751455931266</v>
       </c>
       <c r="D55">
-        <v>6165.557483483165</v>
+        <v>6190.921455931266</v>
       </c>
       <c r="E55">
-        <v>574.6149999999998</v>
+        <v>634.6700000000001</v>
       </c>
       <c r="F55">
-        <v>3182.915</v>
+        <v>3242.97</v>
       </c>
       <c r="G55">
         <v>281.8</v>
@@ -5803,28 +5803,28 @@
         <v>729.875</v>
       </c>
       <c r="M55">
-        <v>195.1126895</v>
+        <v>198.794061</v>
       </c>
       <c r="N55">
-        <v>534.7623105</v>
+        <v>531.0809389999999</v>
       </c>
       <c r="O55">
-        <v>157.7548815975</v>
+        <v>156.668877005</v>
       </c>
       <c r="P55">
-        <v>377.0074289025</v>
+        <v>374.4120619949999</v>
       </c>
       <c r="Q55">
-        <v>553.0074289025</v>
+        <v>550.4120619949999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1572595802439474</v>
+        <v>0.1592844000376488</v>
       </c>
       <c r="T55">
-        <v>1.724244257979573</v>
+        <v>1.755567576218271</v>
       </c>
       <c r="U55">
         <v>0.0613</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.740786936361717</v>
+        <v>3.67151310420687</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09660773401731843</v>
+        <v>0.09639872031998158</v>
       </c>
       <c r="C56">
-        <v>3229.751455931266</v>
+        <v>3195.269975878869</v>
       </c>
       <c r="D56">
-        <v>6190.921455931266</v>
+        <v>6216.494975878869</v>
       </c>
       <c r="E56">
-        <v>634.6700000000001</v>
+        <v>694.7249999999999</v>
       </c>
       <c r="F56">
-        <v>3242.97</v>
+        <v>3303.025</v>
       </c>
       <c r="G56">
         <v>281.8</v>
@@ -5885,28 +5885,28 @@
         <v>729.875</v>
       </c>
       <c r="M56">
-        <v>198.794061</v>
+        <v>202.4754325</v>
       </c>
       <c r="N56">
-        <v>531.0809389999999</v>
+        <v>527.3995675</v>
       </c>
       <c r="O56">
-        <v>156.668877005</v>
+        <v>155.5828724125</v>
       </c>
       <c r="P56">
-        <v>374.4120619949999</v>
+        <v>371.8166950875</v>
       </c>
       <c r="Q56">
-        <v>550.4120619949999</v>
+        <v>547.8166950875</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1592844000376488</v>
+        <v>0.1613992118221813</v>
       </c>
       <c r="T56">
-        <v>1.755567576218271</v>
+        <v>1.788283041934246</v>
       </c>
       <c r="U56">
         <v>0.0613</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.67151310420687</v>
+        <v>3.604758320494018</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09639872031998158</v>
+        <v>0.09618970662264473</v>
       </c>
       <c r="C57">
-        <v>3195.269975878869</v>
+        <v>3161.000650900054</v>
       </c>
       <c r="D57">
-        <v>6216.494975878869</v>
+        <v>6242.280650900054</v>
       </c>
       <c r="E57">
-        <v>694.7249999999999</v>
+        <v>754.7800000000002</v>
       </c>
       <c r="F57">
-        <v>3303.025</v>
+        <v>3363.08</v>
       </c>
       <c r="G57">
         <v>281.8</v>
@@ -5967,28 +5967,28 @@
         <v>729.875</v>
       </c>
       <c r="M57">
-        <v>202.4754325</v>
+        <v>206.156804</v>
       </c>
       <c r="N57">
-        <v>527.3995675</v>
+        <v>523.718196</v>
       </c>
       <c r="O57">
-        <v>155.5828724125</v>
+        <v>154.49686782</v>
       </c>
       <c r="P57">
-        <v>371.8166950875</v>
+        <v>369.22132818</v>
       </c>
       <c r="Q57">
-        <v>547.8166950875</v>
+        <v>545.22132818</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1613992118221813</v>
+        <v>0.1636101514151017</v>
       </c>
       <c r="T57">
-        <v>1.788283041934246</v>
+        <v>1.822485574273673</v>
       </c>
       <c r="U57">
         <v>0.0613</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.604758320494018</v>
+        <v>3.540387636199482</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09618970662264473</v>
+        <v>0.0971058729253079</v>
       </c>
       <c r="C58">
-        <v>3161.000650900054</v>
+        <v>2989.477570190333</v>
       </c>
       <c r="D58">
-        <v>6242.280650900054</v>
+        <v>6130.812570190333</v>
       </c>
       <c r="E58">
-        <v>754.7800000000002</v>
+        <v>814.835</v>
       </c>
       <c r="F58">
-        <v>3363.08</v>
+        <v>3423.135</v>
       </c>
       <c r="G58">
         <v>281.8</v>
@@ -6049,45 +6049,45 @@
         <v>729.875</v>
       </c>
       <c r="M58">
-        <v>206.156804</v>
+        <v>219.4229535</v>
       </c>
       <c r="N58">
-        <v>523.718196</v>
+        <v>510.4520464999999</v>
       </c>
       <c r="O58">
-        <v>154.49686782</v>
+        <v>150.5833537175</v>
       </c>
       <c r="P58">
-        <v>369.22132818</v>
+        <v>359.8686927825</v>
       </c>
       <c r="Q58">
-        <v>545.22132818</v>
+        <v>535.8686927824999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1636101514151017</v>
+        <v>0.1659239254076928</v>
       </c>
       <c r="T58">
-        <v>1.822485574273673</v>
+        <v>1.858278922070749</v>
       </c>
       <c r="U58">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V58">
         <v>0.295</v>
       </c>
       <c r="W58">
-        <v>0.0432165</v>
+        <v>0.04519050000000001</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y58">
-        <v>3.540387636199482</v>
+        <v>3.326338417917612</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.0971058729253079</v>
+        <v>0.09691659922797102</v>
       </c>
       <c r="C59">
-        <v>2989.477570190333</v>
+        <v>2952.123641473735</v>
       </c>
       <c r="D59">
-        <v>6130.812570190333</v>
+        <v>6153.513641473735</v>
       </c>
       <c r="E59">
-        <v>814.835</v>
+        <v>874.8900000000003</v>
       </c>
       <c r="F59">
-        <v>3423.135</v>
+        <v>3483.190000000001</v>
       </c>
       <c r="G59">
         <v>281.8</v>
@@ -6131,28 +6131,28 @@
         <v>729.875</v>
       </c>
       <c r="M59">
-        <v>219.4229535</v>
+        <v>223.2724790000001</v>
       </c>
       <c r="N59">
-        <v>510.4520464999999</v>
+        <v>506.6025209999999</v>
       </c>
       <c r="O59">
-        <v>150.5833537175</v>
+        <v>149.447743695</v>
       </c>
       <c r="P59">
-        <v>359.8686927825</v>
+        <v>357.1547773049999</v>
       </c>
       <c r="Q59">
-        <v>535.8686927824999</v>
+        <v>533.1547773049999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1659239254076928</v>
+        <v>0.1683478791142168</v>
       </c>
       <c r="T59">
-        <v>1.858278922070749</v>
+        <v>1.895776715001019</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.326338417917612</v>
+        <v>3.268987755539722</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09691659922797104</v>
+        <v>0.09672732553063419</v>
       </c>
       <c r="C60">
-        <v>2952.123641473733</v>
+        <v>2914.938451863322</v>
       </c>
       <c r="D60">
-        <v>6153.513641473733</v>
+        <v>6176.383451863322</v>
       </c>
       <c r="E60">
-        <v>874.8899999999994</v>
+        <v>934.9449999999997</v>
       </c>
       <c r="F60">
-        <v>3483.19</v>
+        <v>3543.245</v>
       </c>
       <c r="G60">
         <v>281.8</v>
@@ -6213,28 +6213,28 @@
         <v>729.875</v>
       </c>
       <c r="M60">
-        <v>223.272479</v>
+        <v>227.1220045</v>
       </c>
       <c r="N60">
-        <v>506.602521</v>
+        <v>502.7529955</v>
       </c>
       <c r="O60">
-        <v>149.447743695</v>
+        <v>148.3121336725</v>
       </c>
       <c r="P60">
-        <v>357.154777305</v>
+        <v>354.4408618275</v>
       </c>
       <c r="Q60">
-        <v>533.154777305</v>
+        <v>530.4408618275</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1683478791142167</v>
+        <v>0.1708900744649614</v>
       </c>
       <c r="T60">
-        <v>1.895776715001018</v>
+        <v>1.935103668562033</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.268987755539724</v>
+        <v>3.213581183411931</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09672732553063419</v>
+        <v>0.09653805183329735</v>
       </c>
       <c r="C61">
-        <v>2914.938451863322</v>
+        <v>2877.923889756861</v>
       </c>
       <c r="D61">
-        <v>6176.383451863322</v>
+        <v>6199.42388975686</v>
       </c>
       <c r="E61">
-        <v>934.9449999999997</v>
+        <v>994.9999999999995</v>
       </c>
       <c r="F61">
-        <v>3543.245</v>
+        <v>3603.3</v>
       </c>
       <c r="G61">
         <v>281.8</v>
@@ -6295,28 +6295,28 @@
         <v>729.875</v>
       </c>
       <c r="M61">
-        <v>227.1220045</v>
+        <v>230.97153</v>
       </c>
       <c r="N61">
-        <v>502.7529955</v>
+        <v>498.90347</v>
       </c>
       <c r="O61">
-        <v>148.3121336725</v>
+        <v>147.17652365</v>
       </c>
       <c r="P61">
-        <v>354.4408618275</v>
+        <v>351.72694635</v>
       </c>
       <c r="Q61">
-        <v>530.4408618275</v>
+        <v>527.7269463499999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1708900744649614</v>
+        <v>0.1735593795832433</v>
       </c>
       <c r="T61">
-        <v>1.935103668562033</v>
+        <v>1.976396969801098</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.213581183411931</v>
+        <v>3.160021497021732</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09653805183329735</v>
+        <v>0.09634877813596049</v>
       </c>
       <c r="C62">
-        <v>2877.923889756861</v>
+        <v>2841.081871835611</v>
       </c>
       <c r="D62">
-        <v>6199.42388975686</v>
+        <v>6222.636871835611</v>
       </c>
       <c r="E62">
-        <v>994.9999999999995</v>
+        <v>1055.055</v>
       </c>
       <c r="F62">
-        <v>3603.3</v>
+        <v>3663.355</v>
       </c>
       <c r="G62">
         <v>281.8</v>
@@ -6377,28 +6377,28 @@
         <v>729.875</v>
       </c>
       <c r="M62">
-        <v>230.97153</v>
+        <v>234.8210555</v>
       </c>
       <c r="N62">
-        <v>498.90347</v>
+        <v>495.0539444999999</v>
       </c>
       <c r="O62">
-        <v>147.17652365</v>
+        <v>146.0409136275</v>
       </c>
       <c r="P62">
-        <v>351.72694635</v>
+        <v>349.0130308724999</v>
       </c>
       <c r="Q62">
-        <v>527.7269463499999</v>
+        <v>525.0130308724999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1735593795832433</v>
+        <v>0.1763655721434884</v>
       </c>
       <c r="T62">
-        <v>1.976396969801098</v>
+        <v>2.01980787623191</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.160021497021732</v>
+        <v>3.108217865923015</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09634877813596049</v>
+        <v>0.09615950443862364</v>
       </c>
       <c r="C63">
-        <v>2841.081871835611</v>
+        <v>2804.414343595829</v>
       </c>
       <c r="D63">
-        <v>6222.636871835611</v>
+        <v>6246.024343595829</v>
       </c>
       <c r="E63">
-        <v>1055.055</v>
+        <v>1115.11</v>
       </c>
       <c r="F63">
-        <v>3663.355</v>
+        <v>3723.41</v>
       </c>
       <c r="G63">
         <v>281.8</v>
@@ -6459,28 +6459,28 @@
         <v>729.875</v>
       </c>
       <c r="M63">
-        <v>234.8210555</v>
+        <v>238.670581</v>
       </c>
       <c r="N63">
-        <v>495.0539444999999</v>
+        <v>491.204419</v>
       </c>
       <c r="O63">
-        <v>146.0409136275</v>
+        <v>144.905303605</v>
       </c>
       <c r="P63">
-        <v>349.0130308724999</v>
+        <v>346.2991153950001</v>
       </c>
       <c r="Q63">
-        <v>525.0130308724999</v>
+        <v>522.2991153950001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1763655721434884</v>
+        <v>0.1793194590490096</v>
       </c>
       <c r="T63">
-        <v>2.01980787623191</v>
+        <v>2.065503567211712</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.108217865923015</v>
+        <v>3.058085319698451</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09615950443862364</v>
+        <v>0.09597023074128677</v>
       </c>
       <c r="C64">
-        <v>2804.414343595829</v>
+        <v>2767.923279892331</v>
       </c>
       <c r="D64">
-        <v>6246.024343595829</v>
+        <v>6269.588279892331</v>
       </c>
       <c r="E64">
-        <v>1115.11</v>
+        <v>1175.165</v>
       </c>
       <c r="F64">
-        <v>3723.41</v>
+        <v>3783.465</v>
       </c>
       <c r="G64">
         <v>281.8</v>
@@ -6541,28 +6541,28 @@
         <v>729.875</v>
       </c>
       <c r="M64">
-        <v>238.670581</v>
+        <v>242.5201065</v>
       </c>
       <c r="N64">
-        <v>491.204419</v>
+        <v>487.3548935</v>
       </c>
       <c r="O64">
-        <v>144.905303605</v>
+        <v>143.7696935825</v>
       </c>
       <c r="P64">
-        <v>346.2991153950001</v>
+        <v>343.5851999175</v>
       </c>
       <c r="Q64">
-        <v>522.2991153950001</v>
+        <v>519.5851999174999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1793194590490096</v>
+        <v>0.1824330155169913</v>
       </c>
       <c r="T64">
-        <v>2.065503567211712</v>
+        <v>2.113669295541773</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.058085319698451</v>
+        <v>3.00954428287784</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09597023074128677</v>
+        <v>0.09930031704394995</v>
       </c>
       <c r="C65">
-        <v>2767.923279892331</v>
+        <v>2317.622554113626</v>
       </c>
       <c r="D65">
-        <v>6269.588279892331</v>
+        <v>5879.342554113626</v>
       </c>
       <c r="E65">
-        <v>1175.165</v>
+        <v>1235.22</v>
       </c>
       <c r="F65">
-        <v>3783.465</v>
+        <v>3843.52</v>
       </c>
       <c r="G65">
         <v>281.8</v>
@@ -6623,45 +6623,45 @@
         <v>729.875</v>
       </c>
       <c r="M65">
-        <v>242.5201065</v>
+        <v>276.349088</v>
       </c>
       <c r="N65">
-        <v>487.3548935</v>
+        <v>453.525912</v>
       </c>
       <c r="O65">
-        <v>143.7696935825</v>
+        <v>133.79014404</v>
       </c>
       <c r="P65">
-        <v>343.5851999175</v>
+        <v>319.73576796</v>
       </c>
       <c r="Q65">
-        <v>519.5851999174999</v>
+        <v>495.73576796</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1824330155169913</v>
+        <v>0.1857195473443054</v>
       </c>
       <c r="T65">
-        <v>2.113669295541773</v>
+        <v>2.16451089766795</v>
       </c>
       <c r="U65">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V65">
         <v>0.295</v>
       </c>
       <c r="W65">
-        <v>0.04519050000000001</v>
+        <v>0.05068950000000001</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y65">
-        <v>3.00954428287784</v>
+        <v>2.641134100648814</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09930031704394995</v>
+        <v>0.0991660333466131</v>
       </c>
       <c r="C66">
-        <v>2317.622554113626</v>
+        <v>2272.361605808427</v>
       </c>
       <c r="D66">
-        <v>5879.342554113626</v>
+        <v>5894.136605808427</v>
       </c>
       <c r="E66">
-        <v>1235.22</v>
+        <v>1295.275</v>
       </c>
       <c r="F66">
-        <v>3843.52</v>
+        <v>3903.575</v>
       </c>
       <c r="G66">
         <v>281.8</v>
@@ -6705,28 +6705,28 @@
         <v>729.875</v>
       </c>
       <c r="M66">
-        <v>276.349088</v>
+        <v>280.6670425</v>
       </c>
       <c r="N66">
-        <v>453.525912</v>
+        <v>449.2079575</v>
       </c>
       <c r="O66">
-        <v>133.79014404</v>
+        <v>132.5163474625</v>
       </c>
       <c r="P66">
-        <v>319.73576796</v>
+        <v>316.6916100375</v>
       </c>
       <c r="Q66">
-        <v>495.73576796</v>
+        <v>492.6916100375</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1857195473443054</v>
+        <v>0.1891938809903231</v>
       </c>
       <c r="T66">
-        <v>2.16451089766795</v>
+        <v>2.218257734201337</v>
       </c>
       <c r="U66">
         <v>0.07190000000000001</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.641134100648814</v>
+        <v>2.60050126833114</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.0991660333466131</v>
+        <v>0.09903174964927625</v>
       </c>
       <c r="C67">
-        <v>2272.361605808427</v>
+        <v>2227.175297167461</v>
       </c>
       <c r="D67">
-        <v>5894.136605808427</v>
+        <v>5909.005297167461</v>
       </c>
       <c r="E67">
-        <v>1295.275</v>
+        <v>1355.33</v>
       </c>
       <c r="F67">
-        <v>3903.575</v>
+        <v>3963.63</v>
       </c>
       <c r="G67">
         <v>281.8</v>
@@ -6787,28 +6787,28 @@
         <v>729.875</v>
       </c>
       <c r="M67">
-        <v>280.6670425</v>
+        <v>284.984997</v>
       </c>
       <c r="N67">
-        <v>449.2079575</v>
+        <v>444.890003</v>
       </c>
       <c r="O67">
-        <v>132.5163474625</v>
+        <v>131.242550885</v>
       </c>
       <c r="P67">
-        <v>316.6916100375</v>
+        <v>313.647452115</v>
       </c>
       <c r="Q67">
-        <v>492.6916100375</v>
+        <v>489.647452115</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1891938809903231</v>
+        <v>0.1928725872037537</v>
       </c>
       <c r="T67">
-        <v>2.218257734201337</v>
+        <v>2.275166149354334</v>
       </c>
       <c r="U67">
         <v>0.07190000000000001</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.60050126833114</v>
+        <v>2.561099733962486</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09903174964927625</v>
+        <v>0.09889746595193939</v>
       </c>
       <c r="C68">
-        <v>2227.175297167461</v>
+        <v>2182.064194482728</v>
       </c>
       <c r="D68">
-        <v>5909.005297167461</v>
+        <v>5923.949194482729</v>
       </c>
       <c r="E68">
-        <v>1355.33</v>
+        <v>1415.385</v>
       </c>
       <c r="F68">
-        <v>3963.63</v>
+        <v>4023.685</v>
       </c>
       <c r="G68">
         <v>281.8</v>
@@ -6869,28 +6869,28 @@
         <v>729.875</v>
       </c>
       <c r="M68">
-        <v>284.984997</v>
+        <v>289.3029515000001</v>
       </c>
       <c r="N68">
-        <v>444.890003</v>
+        <v>440.5720484999999</v>
       </c>
       <c r="O68">
-        <v>131.242550885</v>
+        <v>129.9687543075</v>
       </c>
       <c r="P68">
-        <v>313.647452115</v>
+        <v>310.6032941925</v>
       </c>
       <c r="Q68">
-        <v>489.647452115</v>
+        <v>486.6032941925</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1928725872037537</v>
+        <v>0.1967742453089072</v>
       </c>
       <c r="T68">
-        <v>2.275166149354334</v>
+        <v>2.335523559365088</v>
       </c>
       <c r="U68">
         <v>0.07190000000000001</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.561099733962486</v>
+        <v>2.522874364798867</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09889746595193939</v>
+        <v>0.1006328422546025</v>
       </c>
       <c r="C69">
-        <v>2182.064194482728</v>
+        <v>1934.525186220822</v>
       </c>
       <c r="D69">
-        <v>5923.949194482729</v>
+        <v>5736.465186220822</v>
       </c>
       <c r="E69">
-        <v>1415.385</v>
+        <v>1475.44</v>
       </c>
       <c r="F69">
-        <v>4023.685</v>
+        <v>4083.74</v>
       </c>
       <c r="G69">
         <v>281.8</v>
@@ -6951,45 +6951,45 @@
         <v>729.875</v>
       </c>
       <c r="M69">
-        <v>289.3029515000001</v>
+        <v>309.547492</v>
       </c>
       <c r="N69">
-        <v>440.5720484999999</v>
+        <v>420.327508</v>
       </c>
       <c r="O69">
-        <v>129.9687543075</v>
+        <v>123.99661486</v>
       </c>
       <c r="P69">
-        <v>310.6032941925</v>
+        <v>296.33089314</v>
       </c>
       <c r="Q69">
-        <v>486.6032941925</v>
+        <v>472.33089314</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1967742453089072</v>
+        <v>0.2009197570456329</v>
       </c>
       <c r="T69">
-        <v>2.335523559365088</v>
+        <v>2.399653307501515</v>
       </c>
       <c r="U69">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V69">
         <v>0.295</v>
       </c>
       <c r="W69">
-        <v>0.05068950000000001</v>
+        <v>0.05343900000000001</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y69">
-        <v>2.522874364798867</v>
+        <v>2.357877284949865</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1006328422546025</v>
+        <v>0.1005260535572657</v>
       </c>
       <c r="C70">
-        <v>1934.525186220822</v>
+        <v>1885.663934074641</v>
       </c>
       <c r="D70">
-        <v>5736.465186220822</v>
+        <v>5747.658934074641</v>
       </c>
       <c r="E70">
-        <v>1475.44</v>
+        <v>1535.495</v>
       </c>
       <c r="F70">
-        <v>4083.74</v>
+        <v>4143.795</v>
       </c>
       <c r="G70">
         <v>281.8</v>
@@ -7033,28 +7033,28 @@
         <v>729.875</v>
       </c>
       <c r="M70">
-        <v>309.547492</v>
+        <v>314.099661</v>
       </c>
       <c r="N70">
-        <v>420.327508</v>
+        <v>415.775339</v>
       </c>
       <c r="O70">
-        <v>123.99661486</v>
+        <v>122.653725005</v>
       </c>
       <c r="P70">
-        <v>296.33089314</v>
+        <v>293.121613995</v>
       </c>
       <c r="Q70">
-        <v>472.33089314</v>
+        <v>469.121613995</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2009197570456329</v>
+        <v>0.20533272115247</v>
       </c>
       <c r="T70">
-        <v>2.399653307501515</v>
+        <v>2.467920458743518</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.357877284949865</v>
+        <v>2.323705150385374</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1005260535572657</v>
+        <v>0.1004192648599289</v>
       </c>
       <c r="C71">
-        <v>1885.663934074641</v>
+        <v>1836.846452775787</v>
       </c>
       <c r="D71">
-        <v>5747.658934074641</v>
+        <v>5758.896452775787</v>
       </c>
       <c r="E71">
-        <v>1535.495</v>
+        <v>1595.55</v>
       </c>
       <c r="F71">
-        <v>4143.795</v>
+        <v>4203.85</v>
       </c>
       <c r="G71">
         <v>281.8</v>
@@ -7115,28 +7115,28 @@
         <v>729.875</v>
       </c>
       <c r="M71">
-        <v>314.099661</v>
+        <v>318.6518300000001</v>
       </c>
       <c r="N71">
-        <v>415.775339</v>
+        <v>411.2231699999999</v>
       </c>
       <c r="O71">
-        <v>122.653725005</v>
+        <v>121.31083515</v>
       </c>
       <c r="P71">
-        <v>293.121613995</v>
+        <v>289.91233485</v>
       </c>
       <c r="Q71">
-        <v>469.121613995</v>
+        <v>465.91233485</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.20533272115247</v>
+        <v>0.2100398828664295</v>
       </c>
       <c r="T71">
-        <v>2.467920458743518</v>
+        <v>2.540738753401655</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.323705150385374</v>
+        <v>2.290509362522725</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1004192648599289</v>
+        <v>0.100312476162592</v>
       </c>
       <c r="C72">
-        <v>1836.846452775787</v>
+        <v>1788.072999562534</v>
       </c>
       <c r="D72">
-        <v>5758.896452775787</v>
+        <v>5770.177999562535</v>
       </c>
       <c r="E72">
-        <v>1595.55</v>
+        <v>1655.605</v>
       </c>
       <c r="F72">
-        <v>4203.85</v>
+        <v>4263.905000000001</v>
       </c>
       <c r="G72">
         <v>281.8</v>
@@ -7197,28 +7197,28 @@
         <v>729.875</v>
       </c>
       <c r="M72">
-        <v>318.6518300000001</v>
+        <v>323.2039990000001</v>
       </c>
       <c r="N72">
-        <v>411.2231699999999</v>
+        <v>406.6710009999999</v>
       </c>
       <c r="O72">
-        <v>121.31083515</v>
+        <v>119.967945295</v>
       </c>
       <c r="P72">
-        <v>289.91233485</v>
+        <v>286.7030557049999</v>
       </c>
       <c r="Q72">
-        <v>465.91233485</v>
+        <v>462.7030557049999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2100398828664295</v>
+        <v>0.2150716764227311</v>
       </c>
       <c r="T72">
-        <v>2.540738753401655</v>
+        <v>2.618578999415525</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.290509362522725</v>
+        <v>2.258248667275926</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.100312476162592</v>
+        <v>0.1002056874652552</v>
       </c>
       <c r="C73">
-        <v>1788.072999562535</v>
+        <v>1739.343833692808</v>
       </c>
       <c r="D73">
-        <v>5770.177999562535</v>
+        <v>5781.503833692808</v>
       </c>
       <c r="E73">
-        <v>1655.605</v>
+        <v>1715.66</v>
       </c>
       <c r="F73">
-        <v>4263.905</v>
+        <v>4323.96</v>
       </c>
       <c r="G73">
         <v>281.8</v>
@@ -7279,28 +7279,28 @@
         <v>729.875</v>
       </c>
       <c r="M73">
-        <v>323.203999</v>
+        <v>327.756168</v>
       </c>
       <c r="N73">
-        <v>406.671001</v>
+        <v>402.118832</v>
       </c>
       <c r="O73">
-        <v>119.967945295</v>
+        <v>118.62505544</v>
       </c>
       <c r="P73">
-        <v>286.703055705</v>
+        <v>283.49377656</v>
       </c>
       <c r="Q73">
-        <v>462.703055705</v>
+        <v>459.49377656</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.215071676422731</v>
+        <v>0.2204628838044826</v>
       </c>
       <c r="T73">
-        <v>2.618578999415524</v>
+        <v>2.701979263001813</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.258248667275927</v>
+        <v>2.22688410245265</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1002056874652552</v>
+        <v>0.1000988987679183</v>
       </c>
       <c r="C74">
-        <v>1739.343833692808</v>
+        <v>1690.65921646405</v>
       </c>
       <c r="D74">
-        <v>5781.503833692808</v>
+        <v>5792.87421646405</v>
       </c>
       <c r="E74">
-        <v>1715.66</v>
+        <v>1775.715</v>
       </c>
       <c r="F74">
-        <v>4323.96</v>
+        <v>4384.015</v>
       </c>
       <c r="G74">
         <v>281.8</v>
@@ -7361,28 +7361,28 @@
         <v>729.875</v>
       </c>
       <c r="M74">
-        <v>327.756168</v>
+        <v>332.3083370000001</v>
       </c>
       <c r="N74">
-        <v>402.118832</v>
+        <v>397.5666629999999</v>
       </c>
       <c r="O74">
-        <v>118.62505544</v>
+        <v>117.282165585</v>
       </c>
       <c r="P74">
-        <v>283.49377656</v>
+        <v>280.284497415</v>
       </c>
       <c r="Q74">
-        <v>459.49377656</v>
+        <v>456.284497415</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2204628838044826</v>
+        <v>0.2262534398811789</v>
       </c>
       <c r="T74">
-        <v>2.701979263001813</v>
+        <v>2.79155732389079</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.22688410245265</v>
+        <v>2.196378840775216</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1000988987679183</v>
+        <v>0.09999211007058145</v>
       </c>
       <c r="C75">
-        <v>1690.65921646405</v>
+        <v>1642.019411233302</v>
       </c>
       <c r="D75">
-        <v>5792.87421646405</v>
+        <v>5804.289411233302</v>
       </c>
       <c r="E75">
-        <v>1775.715</v>
+        <v>1835.77</v>
       </c>
       <c r="F75">
-        <v>4384.015</v>
+        <v>4444.07</v>
       </c>
       <c r="G75">
         <v>281.8</v>
@@ -7443,28 +7443,28 @@
         <v>729.875</v>
       </c>
       <c r="M75">
-        <v>332.3083370000001</v>
+        <v>336.860506</v>
       </c>
       <c r="N75">
-        <v>397.5666629999999</v>
+        <v>393.014494</v>
       </c>
       <c r="O75">
-        <v>117.282165585</v>
+        <v>115.93927573</v>
       </c>
       <c r="P75">
-        <v>280.284497415</v>
+        <v>277.0752182700001</v>
       </c>
       <c r="Q75">
-        <v>456.284497415</v>
+        <v>453.0752182700001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2262534398811789</v>
+        <v>0.2324894233483902</v>
       </c>
       <c r="T75">
-        <v>2.79155732389079</v>
+        <v>2.88802600484815</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.196378840775216</v>
+        <v>2.166698045629606</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09999211007058145</v>
+        <v>0.0998853213732446</v>
       </c>
       <c r="C76">
-        <v>1642.019411233302</v>
+        <v>1593.424683437551</v>
       </c>
       <c r="D76">
-        <v>5804.289411233302</v>
+        <v>5815.749683437551</v>
       </c>
       <c r="E76">
-        <v>1835.77</v>
+        <v>1895.825</v>
       </c>
       <c r="F76">
-        <v>4444.07</v>
+        <v>4504.125</v>
       </c>
       <c r="G76">
         <v>281.8</v>
@@ -7525,28 +7525,28 @@
         <v>729.875</v>
       </c>
       <c r="M76">
-        <v>336.860506</v>
+        <v>341.412675</v>
       </c>
       <c r="N76">
-        <v>393.014494</v>
+        <v>388.462325</v>
       </c>
       <c r="O76">
-        <v>115.93927573</v>
+        <v>114.596385875</v>
       </c>
       <c r="P76">
-        <v>277.0752182700001</v>
+        <v>273.865939125</v>
       </c>
       <c r="Q76">
-        <v>453.0752182700001</v>
+        <v>449.865939125</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2324894233483902</v>
+        <v>0.2392242854929784</v>
       </c>
       <c r="T76">
-        <v>2.88802600484815</v>
+        <v>2.992212180282099</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.166698045629606</v>
+        <v>2.137808738354544</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.0998853213732446</v>
+        <v>0.09977853267590775</v>
       </c>
       <c r="C77">
-        <v>1593.424683437551</v>
+        <v>1544.875300614298</v>
       </c>
       <c r="D77">
-        <v>5815.749683437551</v>
+        <v>5827.255300614298</v>
       </c>
       <c r="E77">
-        <v>1895.825</v>
+        <v>1955.88</v>
       </c>
       <c r="F77">
-        <v>4504.125</v>
+        <v>4564.18</v>
       </c>
       <c r="G77">
         <v>281.8</v>
@@ -7607,28 +7607,28 @@
         <v>729.875</v>
       </c>
       <c r="M77">
-        <v>341.412675</v>
+        <v>345.964844</v>
       </c>
       <c r="N77">
-        <v>388.462325</v>
+        <v>383.910156</v>
       </c>
       <c r="O77">
-        <v>114.596385875</v>
+        <v>113.25349602</v>
       </c>
       <c r="P77">
-        <v>273.865939125</v>
+        <v>270.65665998</v>
       </c>
       <c r="Q77">
-        <v>449.865939125</v>
+        <v>446.65665998</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2392242854929784</v>
+        <v>0.2465203861496156</v>
       </c>
       <c r="T77">
-        <v>2.992212180282099</v>
+        <v>3.105080537002211</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.137808738354544</v>
+        <v>2.109679676007774</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09977853267590775</v>
+        <v>0.0996717439785709</v>
       </c>
       <c r="C78">
-        <v>1544.875300614298</v>
+        <v>1496.371532422376</v>
       </c>
       <c r="D78">
-        <v>5827.255300614298</v>
+        <v>5838.806532422375</v>
       </c>
       <c r="E78">
-        <v>1955.88</v>
+        <v>2015.934999999999</v>
       </c>
       <c r="F78">
-        <v>4564.18</v>
+        <v>4624.235</v>
       </c>
       <c r="G78">
         <v>281.8</v>
@@ -7689,28 +7689,28 @@
         <v>729.875</v>
       </c>
       <c r="M78">
-        <v>345.964844</v>
+        <v>350.517013</v>
       </c>
       <c r="N78">
-        <v>383.910156</v>
+        <v>379.357987</v>
       </c>
       <c r="O78">
-        <v>113.25349602</v>
+        <v>111.910606165</v>
       </c>
       <c r="P78">
-        <v>270.65665998</v>
+        <v>267.447380835</v>
       </c>
       <c r="Q78">
-        <v>446.65665998</v>
+        <v>443.447380835</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2465203861496156</v>
+        <v>0.2544509303416126</v>
       </c>
       <c r="T78">
-        <v>3.105080537002211</v>
+        <v>3.227763533437114</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.109679676007774</v>
+        <v>2.082281238657023</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.0996717439785709</v>
+        <v>0.09956495528123405</v>
       </c>
       <c r="C79">
-        <v>1496.371532422376</v>
+        <v>1447.913650663016</v>
       </c>
       <c r="D79">
-        <v>5838.806532422375</v>
+        <v>5850.403650663015</v>
       </c>
       <c r="E79">
-        <v>2015.934999999999</v>
+        <v>2075.99</v>
       </c>
       <c r="F79">
-        <v>4624.235</v>
+        <v>4684.29</v>
       </c>
       <c r="G79">
         <v>281.8</v>
@@ -7771,28 +7771,28 @@
         <v>729.875</v>
       </c>
       <c r="M79">
-        <v>350.517013</v>
+        <v>355.069182</v>
       </c>
       <c r="N79">
-        <v>379.357987</v>
+        <v>374.805818</v>
       </c>
       <c r="O79">
-        <v>111.910606165</v>
+        <v>110.56771631</v>
       </c>
       <c r="P79">
-        <v>267.447380835</v>
+        <v>264.23810169</v>
       </c>
       <c r="Q79">
-        <v>443.447380835</v>
+        <v>440.23810169</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2544509303416126</v>
+        <v>0.2631024330965184</v>
       </c>
       <c r="T79">
-        <v>3.227763533437114</v>
+        <v>3.361599529547918</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.082281238657023</v>
+        <v>2.055585325340908</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09956495528123405</v>
+        <v>0.0994581665838972</v>
       </c>
       <c r="C80">
-        <v>1447.913650663016</v>
+        <v>1399.501929301175</v>
       </c>
       <c r="D80">
-        <v>5850.403650663015</v>
+        <v>5862.046929301175</v>
       </c>
       <c r="E80">
-        <v>2075.99</v>
+        <v>2136.045</v>
       </c>
       <c r="F80">
-        <v>4684.29</v>
+        <v>4744.345</v>
       </c>
       <c r="G80">
         <v>281.8</v>
@@ -7853,28 +7853,28 @@
         <v>729.875</v>
       </c>
       <c r="M80">
-        <v>355.069182</v>
+        <v>359.6213510000001</v>
       </c>
       <c r="N80">
-        <v>374.805818</v>
+        <v>370.2536489999999</v>
       </c>
       <c r="O80">
-        <v>110.56771631</v>
+        <v>109.224826455</v>
       </c>
       <c r="P80">
-        <v>264.23810169</v>
+        <v>261.028822545</v>
       </c>
       <c r="Q80">
-        <v>440.23810169</v>
+        <v>437.028822545</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2631024330965184</v>
+        <v>0.2725778884947486</v>
       </c>
       <c r="T80">
-        <v>3.361599529547918</v>
+        <v>3.508181811002609</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.055585325340908</v>
+        <v>2.029565257931529</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.0994581665838972</v>
+        <v>0.09935137788656034</v>
       </c>
       <c r="C81">
-        <v>1399.501929301175</v>
+        <v>1351.136644487097</v>
       </c>
       <c r="D81">
-        <v>5862.046929301175</v>
+        <v>5873.736644487098</v>
       </c>
       <c r="E81">
-        <v>2136.045</v>
+        <v>2196.1</v>
       </c>
       <c r="F81">
-        <v>4744.345</v>
+        <v>4804.400000000001</v>
       </c>
       <c r="G81">
         <v>281.8</v>
@@ -7935,28 +7935,28 @@
         <v>729.875</v>
       </c>
       <c r="M81">
-        <v>359.6213510000001</v>
+        <v>364.1735200000001</v>
       </c>
       <c r="N81">
-        <v>370.2536489999999</v>
+        <v>365.7014799999999</v>
       </c>
       <c r="O81">
-        <v>109.224826455</v>
+        <v>107.8819366</v>
       </c>
       <c r="P81">
-        <v>261.028822545</v>
+        <v>257.8195434</v>
       </c>
       <c r="Q81">
-        <v>437.028822545</v>
+        <v>433.8195434</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2725778884947486</v>
+        <v>0.2830008894328017</v>
       </c>
       <c r="T81">
-        <v>3.508181811002609</v>
+        <v>3.669422320602767</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.029565257931529</v>
+        <v>2.004195692207385</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09935137788656034</v>
+        <v>0.1073534991892235</v>
       </c>
       <c r="C82">
-        <v>1351.136644487097</v>
+        <v>527.4800012305222</v>
       </c>
       <c r="D82">
-        <v>5873.736644487098</v>
+        <v>5110.135001230522</v>
       </c>
       <c r="E82">
-        <v>2196.1</v>
+        <v>2256.155</v>
       </c>
       <c r="F82">
-        <v>4804.400000000001</v>
+        <v>4864.455</v>
       </c>
       <c r="G82">
         <v>281.8</v>
@@ -8017,45 +8017,45 @@
         <v>729.875</v>
       </c>
       <c r="M82">
-        <v>364.1735200000001</v>
+        <v>437.80095</v>
       </c>
       <c r="N82">
-        <v>365.7014799999999</v>
+        <v>292.07405</v>
       </c>
       <c r="O82">
-        <v>107.8819366</v>
+        <v>86.16184475</v>
       </c>
       <c r="P82">
-        <v>257.8195434</v>
+        <v>205.91220525</v>
       </c>
       <c r="Q82">
-        <v>433.8195434</v>
+        <v>381.91220525</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2830008894328017</v>
+        <v>0.2945210483643342</v>
       </c>
       <c r="T82">
-        <v>3.669422320602767</v>
+        <v>3.847635515423996</v>
       </c>
       <c r="U82">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V82">
         <v>0.295</v>
       </c>
       <c r="W82">
-        <v>0.05343900000000001</v>
+        <v>0.06345000000000001</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y82">
-        <v>2.004195692207385</v>
+        <v>1.667138913243564</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1073534991892235</v>
+        <v>0.1073468204918866</v>
       </c>
       <c r="C83">
-        <v>527.4800012305222</v>
+        <v>467.9795228898211</v>
       </c>
       <c r="D83">
-        <v>5110.135001230522</v>
+        <v>5110.689522889821</v>
       </c>
       <c r="E83">
-        <v>2256.155</v>
+        <v>2316.21</v>
       </c>
       <c r="F83">
-        <v>4864.455</v>
+        <v>4924.51</v>
       </c>
       <c r="G83">
         <v>281.8</v>
@@ -8099,28 +8099,28 @@
         <v>729.875</v>
       </c>
       <c r="M83">
-        <v>437.80095</v>
+        <v>443.2059</v>
       </c>
       <c r="N83">
-        <v>292.07405</v>
+        <v>286.6691</v>
       </c>
       <c r="O83">
-        <v>86.16184475</v>
+        <v>84.5673845</v>
       </c>
       <c r="P83">
-        <v>205.91220525</v>
+        <v>202.1017155</v>
       </c>
       <c r="Q83">
-        <v>381.91220525</v>
+        <v>378.1017155</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2945210483643342</v>
+        <v>0.3073212249549258</v>
       </c>
       <c r="T83">
-        <v>3.847635515423996</v>
+        <v>4.045650176336472</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.667138913243564</v>
+        <v>1.646807950886935</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1073468204918866</v>
+        <v>0.1073401417945498</v>
       </c>
       <c r="C84">
-        <v>467.9795228898211</v>
+        <v>408.4791649090066</v>
       </c>
       <c r="D84">
-        <v>5110.689522889821</v>
+        <v>5111.244164909007</v>
       </c>
       <c r="E84">
-        <v>2316.21</v>
+        <v>2376.265</v>
       </c>
       <c r="F84">
-        <v>4924.51</v>
+        <v>4984.565000000001</v>
       </c>
       <c r="G84">
         <v>281.8</v>
@@ -8181,28 +8181,28 @@
         <v>729.875</v>
       </c>
       <c r="M84">
-        <v>443.2059</v>
+        <v>448.61085</v>
       </c>
       <c r="N84">
-        <v>286.6691</v>
+        <v>281.26415</v>
       </c>
       <c r="O84">
-        <v>84.5673845</v>
+        <v>82.97292424999999</v>
       </c>
       <c r="P84">
-        <v>202.1017155</v>
+        <v>198.29122575</v>
       </c>
       <c r="Q84">
-        <v>378.1017155</v>
+        <v>374.29122575</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3073212249549258</v>
+        <v>0.3216273046738224</v>
       </c>
       <c r="T84">
-        <v>4.045650176336472</v>
+        <v>4.26696067970924</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.646807950886935</v>
+        <v>1.626966891237695</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1073401417945498</v>
+        <v>0.1073334630972129</v>
       </c>
       <c r="C85">
-        <v>408.4791649090066</v>
+        <v>348.9789273272727</v>
       </c>
       <c r="D85">
-        <v>5111.244164909007</v>
+        <v>5111.798927327273</v>
       </c>
       <c r="E85">
-        <v>2376.265</v>
+        <v>2436.320000000001</v>
       </c>
       <c r="F85">
-        <v>4984.565000000001</v>
+        <v>5044.620000000001</v>
       </c>
       <c r="G85">
         <v>281.8</v>
@@ -8263,28 +8263,28 @@
         <v>729.875</v>
       </c>
       <c r="M85">
-        <v>448.61085</v>
+        <v>454.0158000000001</v>
       </c>
       <c r="N85">
-        <v>281.26415</v>
+        <v>275.8591999999999</v>
       </c>
       <c r="O85">
-        <v>82.97292424999999</v>
+        <v>81.37846399999998</v>
       </c>
       <c r="P85">
-        <v>198.29122575</v>
+        <v>194.480736</v>
       </c>
       <c r="Q85">
-        <v>374.29122575</v>
+        <v>370.480736</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3216273046738224</v>
+        <v>0.3377216443575811</v>
       </c>
       <c r="T85">
-        <v>4.26696067970924</v>
+        <v>4.515934996003605</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.626966891237695</v>
+        <v>1.60759823777058</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1073334630972129</v>
+        <v>0.1073267843998761</v>
       </c>
       <c r="C86">
-        <v>348.9789273272736</v>
+        <v>289.4788101838285</v>
       </c>
       <c r="D86">
-        <v>5111.798927327273</v>
+        <v>5112.353810183829</v>
       </c>
       <c r="E86">
-        <v>2436.32</v>
+        <v>2496.375</v>
       </c>
       <c r="F86">
-        <v>5044.62</v>
+        <v>5104.675</v>
       </c>
       <c r="G86">
         <v>281.8</v>
@@ -8345,28 +8345,28 @@
         <v>729.875</v>
       </c>
       <c r="M86">
-        <v>454.0158</v>
+        <v>459.42075</v>
       </c>
       <c r="N86">
-        <v>275.8592</v>
+        <v>270.45425</v>
       </c>
       <c r="O86">
-        <v>81.37846400000001</v>
+        <v>79.78400375</v>
       </c>
       <c r="P86">
-        <v>194.480736</v>
+        <v>190.67024625</v>
       </c>
       <c r="Q86">
-        <v>370.480736</v>
+        <v>366.67024625</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3377216443575808</v>
+        <v>0.3559618959991739</v>
       </c>
       <c r="T86">
-        <v>4.515934996003601</v>
+        <v>4.79810588780388</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.60759823777058</v>
+        <v>1.58868531732622</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1073267843998761</v>
+        <v>0.1073201057025392</v>
       </c>
       <c r="C87">
-        <v>289.4788101838285</v>
+        <v>229.9788135178969</v>
       </c>
       <c r="D87">
-        <v>5112.353810183829</v>
+        <v>5112.908813517896</v>
       </c>
       <c r="E87">
-        <v>2496.375</v>
+        <v>2556.429999999999</v>
       </c>
       <c r="F87">
-        <v>5104.675</v>
+        <v>5164.73</v>
       </c>
       <c r="G87">
         <v>281.8</v>
@@ -8427,28 +8427,28 @@
         <v>729.875</v>
       </c>
       <c r="M87">
-        <v>459.42075</v>
+        <v>464.8256999999999</v>
       </c>
       <c r="N87">
-        <v>270.45425</v>
+        <v>265.0493000000001</v>
       </c>
       <c r="O87">
-        <v>79.78400375</v>
+        <v>78.18954350000001</v>
       </c>
       <c r="P87">
-        <v>190.67024625</v>
+        <v>186.8597565000001</v>
       </c>
       <c r="Q87">
-        <v>366.67024625</v>
+        <v>362.8597565000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3559618959991739</v>
+        <v>0.3768078978752803</v>
       </c>
       <c r="T87">
-        <v>4.79810588780388</v>
+        <v>5.120586907004197</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.58868531732622</v>
+        <v>1.570212232241032</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1073201057025392</v>
+        <v>0.1073134270052024</v>
       </c>
       <c r="C88">
-        <v>229.9788135178969</v>
+        <v>170.4789373687181</v>
       </c>
       <c r="D88">
-        <v>5112.908813517896</v>
+        <v>5113.463937368718</v>
       </c>
       <c r="E88">
-        <v>2556.429999999999</v>
+        <v>2616.485</v>
       </c>
       <c r="F88">
-        <v>5164.73</v>
+        <v>5224.785</v>
       </c>
       <c r="G88">
         <v>281.8</v>
@@ -8509,28 +8509,28 @@
         <v>729.875</v>
       </c>
       <c r="M88">
-        <v>464.8256999999999</v>
+        <v>470.23065</v>
       </c>
       <c r="N88">
-        <v>265.0493000000001</v>
+        <v>259.64435</v>
       </c>
       <c r="O88">
-        <v>78.18954350000001</v>
+        <v>76.59508325</v>
       </c>
       <c r="P88">
-        <v>186.8597565000001</v>
+        <v>183.04926675</v>
       </c>
       <c r="Q88">
-        <v>362.8597565000001</v>
+        <v>359.04926675</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3768078978752803</v>
+        <v>0.4008609769630953</v>
       </c>
       <c r="T88">
-        <v>5.120586907004197</v>
+        <v>5.492680390696872</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.570212232241032</v>
+        <v>1.552163815778491</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1073134270052024</v>
+        <v>0.1073067483078655</v>
       </c>
       <c r="C89">
-        <v>170.4789373687181</v>
+        <v>110.979181775554</v>
       </c>
       <c r="D89">
-        <v>5113.463937368718</v>
+        <v>5114.019181775554</v>
       </c>
       <c r="E89">
-        <v>2616.485</v>
+        <v>2676.54</v>
       </c>
       <c r="F89">
-        <v>5224.785</v>
+        <v>5284.84</v>
       </c>
       <c r="G89">
         <v>281.8</v>
@@ -8591,28 +8591,28 @@
         <v>729.875</v>
       </c>
       <c r="M89">
-        <v>470.23065</v>
+        <v>475.6356</v>
       </c>
       <c r="N89">
-        <v>259.64435</v>
+        <v>254.2394</v>
       </c>
       <c r="O89">
-        <v>76.59508325</v>
+        <v>75.00062299999999</v>
       </c>
       <c r="P89">
-        <v>183.04926675</v>
+        <v>179.238777</v>
       </c>
       <c r="Q89">
-        <v>359.04926675</v>
+        <v>355.238777</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4008609769630953</v>
+        <v>0.4289229025655462</v>
       </c>
       <c r="T89">
-        <v>5.492680390696872</v>
+        <v>5.926789455004993</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.552163815778491</v>
+        <v>1.53452559059919</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1073067483078655</v>
+        <v>0.1073000696105287</v>
       </c>
       <c r="C90">
-        <v>110.979181775554</v>
+        <v>51.47954677767757</v>
       </c>
       <c r="D90">
-        <v>5114.019181775554</v>
+        <v>5114.574546777678</v>
       </c>
       <c r="E90">
-        <v>2676.54</v>
+        <v>2736.595</v>
       </c>
       <c r="F90">
-        <v>5284.84</v>
+        <v>5344.895</v>
       </c>
       <c r="G90">
         <v>281.8</v>
@@ -8673,28 +8673,28 @@
         <v>729.875</v>
       </c>
       <c r="M90">
-        <v>475.6356</v>
+        <v>481.04055</v>
       </c>
       <c r="N90">
-        <v>254.2394</v>
+        <v>248.83445</v>
       </c>
       <c r="O90">
-        <v>75.00062299999999</v>
+        <v>73.40616274999999</v>
       </c>
       <c r="P90">
-        <v>179.238777</v>
+        <v>175.42828725</v>
       </c>
       <c r="Q90">
-        <v>355.238777</v>
+        <v>351.42828725</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4289229025655462</v>
+        <v>0.4620869964593518</v>
       </c>
       <c r="T90">
-        <v>5.926789455004993</v>
+        <v>6.439827440096408</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.53452559059919</v>
+        <v>1.51728373003066</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1073000696105287</v>
+        <v>0.1072933909131918</v>
       </c>
       <c r="C91">
-        <v>51.47954677767757</v>
+        <v>-8.019967585613813</v>
       </c>
       <c r="D91">
-        <v>5114.574546777678</v>
+        <v>5115.130032414386</v>
       </c>
       <c r="E91">
-        <v>2736.595</v>
+        <v>2796.65</v>
       </c>
       <c r="F91">
-        <v>5344.895</v>
+        <v>5404.95</v>
       </c>
       <c r="G91">
         <v>281.8</v>
@@ -8755,28 +8755,28 @@
         <v>729.875</v>
       </c>
       <c r="M91">
-        <v>481.04055</v>
+        <v>486.4455</v>
       </c>
       <c r="N91">
-        <v>248.83445</v>
+        <v>243.4295</v>
       </c>
       <c r="O91">
-        <v>73.40616274999999</v>
+        <v>71.8117025</v>
       </c>
       <c r="P91">
-        <v>175.42828725</v>
+        <v>171.6177975</v>
       </c>
       <c r="Q91">
-        <v>351.42828725</v>
+        <v>347.6177975000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4620869964593518</v>
+        <v>0.5018839091319185</v>
       </c>
       <c r="T91">
-        <v>6.439827440096408</v>
+        <v>7.055473022206107</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.51728373003066</v>
+        <v>1.500425021919208</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1072933909131918</v>
+        <v>0.1487866147922497</v>
       </c>
       <c r="C92">
-        <v>-8.019967585613813</v>
+        <v>-2128.956724245073</v>
       </c>
       <c r="D92">
-        <v>5115.130032414386</v>
+        <v>3054.248275754926</v>
       </c>
       <c r="E92">
-        <v>2796.65</v>
+        <v>2856.705</v>
       </c>
       <c r="F92">
-        <v>5404.95</v>
+        <v>5465.005</v>
       </c>
       <c r="G92">
         <v>281.8</v>
@@ -8837,45 +8837,45 @@
         <v>729.875</v>
       </c>
       <c r="M92">
-        <v>486.4455</v>
+        <v>802.2627340000001</v>
       </c>
       <c r="N92">
-        <v>243.4295</v>
+        <v>-72.38773400000014</v>
       </c>
       <c r="O92">
-        <v>71.8117025</v>
+        <v>-21.35438153000004</v>
       </c>
       <c r="P92">
-        <v>171.6177975</v>
+        <v>-51.0333524700001</v>
       </c>
       <c r="Q92">
-        <v>347.6177975000001</v>
+        <v>124.9666475299999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5018839091319185</v>
+        <v>0.5672363410112131</v>
       </c>
       <c r="T92">
-        <v>7.055473022206107</v>
+        <v>8.066454358814847</v>
       </c>
       <c r="U92">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.295</v>
+        <v>0.2683823090304478</v>
       </c>
       <c r="W92">
-        <v>0.06345000000000001</v>
+        <v>0.1074014770343303</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y92">
-        <v>1.500425021919208</v>
+        <v>0.9097705390862638</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1487866147922497</v>
+        <v>0.1497966147922497</v>
       </c>
       <c r="C93">
-        <v>-2128.956724245073</v>
+        <v>-2218.674139359978</v>
       </c>
       <c r="D93">
-        <v>3054.248275754926</v>
+        <v>3024.585860640022</v>
       </c>
       <c r="E93">
-        <v>2856.705</v>
+        <v>2916.76</v>
       </c>
       <c r="F93">
-        <v>5465.005</v>
+        <v>5525.06</v>
       </c>
       <c r="G93">
         <v>281.8</v>
@@ -8919,37 +8919,37 @@
         <v>729.875</v>
       </c>
       <c r="M93">
-        <v>802.2627340000001</v>
+        <v>811.0788080000001</v>
       </c>
       <c r="N93">
-        <v>-72.38773400000014</v>
+        <v>-81.20380800000009</v>
       </c>
       <c r="O93">
-        <v>-21.35438153000004</v>
+        <v>-23.95512336000003</v>
       </c>
       <c r="P93">
-        <v>-51.0333524700001</v>
+        <v>-57.24868464000006</v>
       </c>
       <c r="Q93">
-        <v>124.9666475299999</v>
+        <v>118.7513153599999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5672363410112131</v>
+        <v>0.6324158836376148</v>
       </c>
       <c r="T93">
-        <v>8.066454358814847</v>
+        <v>9.074761153666703</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.2683823090304478</v>
+        <v>0.2654651100192473</v>
       </c>
       <c r="W93">
-        <v>0.1074014770343303</v>
+        <v>0.1078297218491745</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.9097705390862638</v>
+        <v>0.8998817288788045</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1497966147922497</v>
+        <v>0.1508066147922497</v>
       </c>
       <c r="C94">
-        <v>-2218.674139359978</v>
+        <v>-2307.820942055364</v>
       </c>
       <c r="D94">
-        <v>3024.585860640022</v>
+        <v>2995.494057944637</v>
       </c>
       <c r="E94">
-        <v>2916.76</v>
+        <v>2976.815000000001</v>
       </c>
       <c r="F94">
-        <v>5525.06</v>
+        <v>5585.115000000001</v>
       </c>
       <c r="G94">
         <v>281.8</v>
@@ -9001,37 +9001,37 @@
         <v>729.875</v>
       </c>
       <c r="M94">
-        <v>811.0788080000001</v>
+        <v>819.8948820000002</v>
       </c>
       <c r="N94">
-        <v>-81.20380800000009</v>
+        <v>-90.01988200000017</v>
       </c>
       <c r="O94">
-        <v>-23.95512336000003</v>
+        <v>-26.55586519000005</v>
       </c>
       <c r="P94">
-        <v>-57.24868464000006</v>
+        <v>-63.46401681000012</v>
       </c>
       <c r="Q94">
-        <v>118.7513153599999</v>
+        <v>112.5359831899999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6324158836376148</v>
+        <v>0.7162181527287029</v>
       </c>
       <c r="T94">
-        <v>9.074761153666703</v>
+        <v>10.37115560419052</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.2654651100192473</v>
+        <v>0.2626106464706532</v>
       </c>
       <c r="W94">
-        <v>0.1078297218491745</v>
+        <v>0.1082487570981081</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8998817288788045</v>
+        <v>0.8902055812564517</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1508066147922497</v>
+        <v>0.1518166147922497</v>
       </c>
       <c r="C95">
-        <v>-2307.820942055364</v>
+        <v>-2396.413440677185</v>
       </c>
       <c r="D95">
-        <v>2995.494057944637</v>
+        <v>2966.956559322815</v>
       </c>
       <c r="E95">
-        <v>2976.815000000001</v>
+        <v>3036.87</v>
       </c>
       <c r="F95">
-        <v>5585.115000000001</v>
+        <v>5645.17</v>
       </c>
       <c r="G95">
         <v>281.8</v>
@@ -9083,37 +9083,37 @@
         <v>729.875</v>
       </c>
       <c r="M95">
-        <v>819.8948820000002</v>
+        <v>828.7109560000001</v>
       </c>
       <c r="N95">
-        <v>-90.01988200000017</v>
+        <v>-98.83595600000012</v>
       </c>
       <c r="O95">
-        <v>-26.55586519000005</v>
+        <v>-29.15660702000003</v>
       </c>
       <c r="P95">
-        <v>-63.46401681000012</v>
+        <v>-69.67934898000009</v>
       </c>
       <c r="Q95">
-        <v>112.5359831899999</v>
+        <v>106.3206510199999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7162181527287029</v>
+        <v>0.8279545115168202</v>
       </c>
       <c r="T95">
-        <v>10.37115560419052</v>
+        <v>12.09968153822228</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2626106464706532</v>
+        <v>0.2598169161890506</v>
       </c>
       <c r="W95">
-        <v>0.1082487570981081</v>
+        <v>0.1086588767034474</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8902055812564517</v>
+        <v>0.8807353091154256</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1518166147922497</v>
+        <v>0.1528266147922497</v>
       </c>
       <c r="C96">
-        <v>-2396.413440677185</v>
+        <v>-2484.467327970153</v>
       </c>
       <c r="D96">
-        <v>2966.956559322815</v>
+        <v>2938.957672029847</v>
       </c>
       <c r="E96">
-        <v>3036.87</v>
+        <v>3096.925</v>
       </c>
       <c r="F96">
-        <v>5645.17</v>
+        <v>5705.225</v>
       </c>
       <c r="G96">
         <v>281.8</v>
@@ -9165,37 +9165,37 @@
         <v>729.875</v>
       </c>
       <c r="M96">
-        <v>828.7109560000001</v>
+        <v>837.5270300000001</v>
       </c>
       <c r="N96">
-        <v>-98.83595600000012</v>
+        <v>-107.6520300000001</v>
       </c>
       <c r="O96">
-        <v>-29.15660702000003</v>
+        <v>-31.75734885000002</v>
       </c>
       <c r="P96">
-        <v>-69.67934898000009</v>
+        <v>-75.89468115000005</v>
       </c>
       <c r="Q96">
-        <v>106.3206510199999</v>
+        <v>100.1053188499999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8279545115168202</v>
+        <v>0.9843854138201847</v>
       </c>
       <c r="T96">
-        <v>12.09968153822228</v>
+        <v>14.51961784586674</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.2598169161890506</v>
+        <v>0.2570820012817974</v>
       </c>
       <c r="W96">
-        <v>0.1086588767034474</v>
+        <v>0.1090603622118322</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8807353091154256</v>
+        <v>0.8714644111247369</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1528266147922497</v>
+        <v>0.1538366147922497</v>
       </c>
       <c r="C97">
-        <v>-2484.467327970153</v>
+        <v>-2571.997709853029</v>
       </c>
       <c r="D97">
-        <v>2938.957672029847</v>
+        <v>2911.482290146972</v>
       </c>
       <c r="E97">
-        <v>3096.925</v>
+        <v>3156.98</v>
       </c>
       <c r="F97">
-        <v>5705.225</v>
+        <v>5765.280000000001</v>
       </c>
       <c r="G97">
         <v>281.8</v>
@@ -9247,37 +9247,37 @@
         <v>729.875</v>
       </c>
       <c r="M97">
-        <v>837.5270300000001</v>
+        <v>846.3431040000002</v>
       </c>
       <c r="N97">
-        <v>-107.6520300000001</v>
+        <v>-116.4681040000002</v>
       </c>
       <c r="O97">
-        <v>-31.75734885000002</v>
+        <v>-34.35809068000005</v>
       </c>
       <c r="P97">
-        <v>-75.89468115000005</v>
+        <v>-82.11001332000011</v>
       </c>
       <c r="Q97">
-        <v>100.1053188499999</v>
+        <v>93.88998667999989</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9843854138201847</v>
+        <v>1.219031767275232</v>
       </c>
       <c r="T97">
-        <v>14.51961784586674</v>
+        <v>18.14952230733343</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.2570820012817974</v>
+        <v>0.2544040637684453</v>
       </c>
       <c r="W97">
-        <v>0.1090603622118322</v>
+        <v>0.1094534834387922</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8714644111247369</v>
+        <v>0.8623866568421876</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1538366147922497</v>
+        <v>0.1548466147922497</v>
       </c>
       <c r="C98">
-        <v>-2571.997709853027</v>
+        <v>-2659.019132594814</v>
       </c>
       <c r="D98">
-        <v>2911.482290146972</v>
+        <v>2884.515867405186</v>
       </c>
       <c r="E98">
-        <v>3156.98</v>
+        <v>3217.035</v>
       </c>
       <c r="F98">
-        <v>5765.28</v>
+        <v>5825.335</v>
       </c>
       <c r="G98">
         <v>281.8</v>
@@ -9329,37 +9329,37 @@
         <v>729.875</v>
       </c>
       <c r="M98">
-        <v>846.343104</v>
+        <v>855.1591780000001</v>
       </c>
       <c r="N98">
-        <v>-116.468104</v>
+        <v>-125.2841780000001</v>
       </c>
       <c r="O98">
-        <v>-34.35809068000001</v>
+        <v>-36.95883251000003</v>
       </c>
       <c r="P98">
-        <v>-82.11001332000004</v>
+        <v>-88.32534549000007</v>
       </c>
       <c r="Q98">
-        <v>93.88998667999996</v>
+        <v>87.67465450999993</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.219031767275228</v>
+        <v>1.610109023033638</v>
       </c>
       <c r="T98">
-        <v>18.14952230733338</v>
+        <v>24.19936307644451</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.2544040637684454</v>
+        <v>0.2517813414615541</v>
       </c>
       <c r="W98">
-        <v>0.1094534834387922</v>
+        <v>0.1098384990734439</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8623866568421876</v>
+        <v>0.853496072751031</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1548466147922497</v>
+        <v>0.1558566147922497</v>
       </c>
       <c r="C99">
-        <v>-2659.019132594814</v>
+        <v>-2745.545608494546</v>
       </c>
       <c r="D99">
-        <v>2884.515867405186</v>
+        <v>2858.044391505454</v>
       </c>
       <c r="E99">
-        <v>3217.035</v>
+        <v>3277.09</v>
       </c>
       <c r="F99">
-        <v>5825.335</v>
+        <v>5885.39</v>
       </c>
       <c r="G99">
         <v>281.8</v>
@@ -9411,37 +9411,37 @@
         <v>729.875</v>
       </c>
       <c r="M99">
-        <v>855.1591780000001</v>
+        <v>863.9752520000002</v>
       </c>
       <c r="N99">
-        <v>-125.2841780000001</v>
+        <v>-134.1002520000002</v>
       </c>
       <c r="O99">
-        <v>-36.95883251000003</v>
+        <v>-39.55957434000005</v>
       </c>
       <c r="P99">
-        <v>-88.32534549000007</v>
+        <v>-94.54067766000013</v>
       </c>
       <c r="Q99">
-        <v>87.67465450999993</v>
+        <v>81.45932233999987</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.610109023033638</v>
+        <v>2.392263534550456</v>
       </c>
       <c r="T99">
-        <v>24.19936307644451</v>
+        <v>36.29904461466676</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.2517813414615541</v>
+        <v>0.2492121440997015</v>
       </c>
       <c r="W99">
-        <v>0.1098384990734439</v>
+        <v>0.1102156572461638</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.853496072751031</v>
+        <v>0.8447869291515306</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1558566147922497</v>
+        <v>0.1568666147922497</v>
       </c>
       <c r="C100">
-        <v>-2745.545608494546</v>
+        <v>-2831.590640159956</v>
       </c>
       <c r="D100">
-        <v>2858.044391505454</v>
+        <v>2832.054359840043</v>
       </c>
       <c r="E100">
-        <v>3277.09</v>
+        <v>3337.145</v>
       </c>
       <c r="F100">
-        <v>5885.39</v>
+        <v>5945.445</v>
       </c>
       <c r="G100">
         <v>281.8</v>
@@ -9493,37 +9493,37 @@
         <v>729.875</v>
       </c>
       <c r="M100">
-        <v>863.9752520000002</v>
+        <v>872.791326</v>
       </c>
       <c r="N100">
-        <v>-134.1002520000002</v>
+        <v>-142.916326</v>
       </c>
       <c r="O100">
-        <v>-39.55957434000005</v>
+        <v>-42.16031617000001</v>
       </c>
       <c r="P100">
-        <v>-94.54067766000013</v>
+        <v>-100.75600983</v>
       </c>
       <c r="Q100">
-        <v>81.45932233999987</v>
+        <v>75.24399016999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.392263534550456</v>
+        <v>4.738727069100912</v>
       </c>
       <c r="T100">
-        <v>36.29904461466676</v>
+        <v>72.59808922933352</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.2492121440997015</v>
+        <v>0.2466948497148561</v>
       </c>
       <c r="W100">
-        <v>0.1102156572461638</v>
+        <v>0.1105851960618591</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8447869291515306</v>
+        <v>0.8362537278469699</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1568666147922497</v>
-      </c>
-      <c r="C101">
-        <v>-2831.590640159956</v>
-      </c>
-      <c r="D101">
-        <v>2832.054359840043</v>
-      </c>
-      <c r="E101">
-        <v>3337.145</v>
-      </c>
-      <c r="F101">
-        <v>5945.445</v>
-      </c>
-      <c r="G101">
-        <v>281.8</v>
-      </c>
-      <c r="H101">
-        <v>3397.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>905.875</v>
-      </c>
-      <c r="K101">
-        <v>176</v>
-      </c>
-      <c r="L101">
-        <v>729.875</v>
-      </c>
-      <c r="M101">
-        <v>872.791326</v>
-      </c>
-      <c r="N101">
-        <v>-142.916326</v>
-      </c>
-      <c r="O101">
-        <v>-42.16031617000001</v>
-      </c>
-      <c r="P101">
-        <v>-100.75600983</v>
-      </c>
-      <c r="Q101">
-        <v>75.24399016999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.738727069100912</v>
-      </c>
-      <c r="T101">
-        <v>72.59808922933352</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.2466948497148561</v>
-      </c>
-      <c r="W101">
-        <v>0.1105851960618591</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8362537278469699</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
